--- a/static/sample-data/planning/synth_otc_pharma.xlsx
+++ b/static/sample-data/planning/synth_otc_pharma.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Дата</t>
   </si>
@@ -46,19 +46,10 @@
     <t>Детейлинг контакты</t>
   </si>
   <si>
-    <t>Диджитал бюджет</t>
-  </si>
-  <si>
-    <t>Диджитал клики</t>
-  </si>
-  <si>
     <t>Активность конкурентов</t>
   </si>
   <si>
     <t>Температура</t>
-  </si>
-  <si>
-    <t>Продажи категории</t>
   </si>
 </sst>
 </file>
@@ -394,10 +385,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,2690 +425,2633 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>44227</v>
       </c>
       <c r="B2">
-        <v>205845</v>
+        <v>949283</v>
       </c>
       <c r="C2">
-        <v>16867865</v>
+        <v>17641040</v>
       </c>
       <c r="D2">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E2">
-        <v>329170</v>
+        <v>9990727</v>
       </c>
       <c r="F2">
-        <v>1326092</v>
+        <v>41533780</v>
       </c>
       <c r="G2">
-        <v>79206041</v>
+        <v>58854554</v>
       </c>
       <c r="H2">
-        <v>199009649</v>
+        <v>143346675</v>
       </c>
       <c r="I2">
-        <v>12805829</v>
+        <v>9840605</v>
       </c>
       <c r="J2">
-        <v>3571</v>
+        <v>2805</v>
       </c>
       <c r="K2">
-        <v>4262944</v>
+        <v>140.3</v>
       </c>
       <c r="L2">
-        <v>129005</v>
-      </c>
-      <c r="M2">
-        <v>196.9</v>
-      </c>
-      <c r="N2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O2">
-        <v>965019</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>8.859999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>44255</v>
       </c>
       <c r="B3">
-        <v>199035</v>
+        <v>1064971</v>
       </c>
       <c r="C3">
-        <v>510127</v>
+        <v>21471519</v>
       </c>
       <c r="D3">
-        <v>2.8</v>
+        <v>118.3</v>
       </c>
       <c r="E3">
-        <v>1494290</v>
+        <v>8658030</v>
       </c>
       <c r="F3">
-        <v>5751481</v>
+        <v>35968913</v>
       </c>
       <c r="G3">
-        <v>32068342</v>
+        <v>80883027</v>
       </c>
       <c r="H3">
-        <v>79468835</v>
+        <v>193123061</v>
       </c>
       <c r="I3">
-        <v>10459119</v>
+        <v>13361515</v>
       </c>
       <c r="J3">
-        <v>3039</v>
+        <v>3744</v>
       </c>
       <c r="K3">
-        <v>2524167</v>
+        <v>162.7</v>
       </c>
       <c r="L3">
-        <v>74550</v>
-      </c>
-      <c r="M3">
-        <v>199.3</v>
-      </c>
-      <c r="N3">
-        <v>3.68</v>
-      </c>
-      <c r="O3">
-        <v>925407</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>44286</v>
       </c>
       <c r="B4">
-        <v>194632</v>
+        <v>1075622</v>
       </c>
       <c r="C4">
-        <v>16719484</v>
+        <v>9949849</v>
       </c>
       <c r="D4">
-        <v>92</v>
+        <v>53.9</v>
       </c>
       <c r="E4">
-        <v>4729177</v>
+        <v>10224360</v>
       </c>
       <c r="F4">
-        <v>18628288</v>
+        <v>40755909</v>
       </c>
       <c r="G4">
-        <v>29705598</v>
+        <v>495312</v>
       </c>
       <c r="H4">
-        <v>76659444</v>
+        <v>1223270</v>
       </c>
       <c r="I4">
-        <v>4901900</v>
+        <v>15522515</v>
       </c>
       <c r="J4">
-        <v>1442</v>
+        <v>4492</v>
       </c>
       <c r="K4">
-        <v>1248369</v>
+        <v>208.5</v>
       </c>
       <c r="L4">
-        <v>36262</v>
-      </c>
-      <c r="M4">
-        <v>48.1</v>
-      </c>
-      <c r="N4">
-        <v>8.85</v>
-      </c>
-      <c r="O4">
-        <v>798970</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>44316</v>
       </c>
       <c r="B5">
-        <v>191422</v>
+        <v>1079551</v>
       </c>
       <c r="C5">
-        <v>25629542</v>
+        <v>14913865</v>
       </c>
       <c r="D5">
-        <v>145.2</v>
+        <v>78.2</v>
       </c>
       <c r="E5">
-        <v>3884025</v>
+        <v>5918930</v>
       </c>
       <c r="F5">
-        <v>15149131</v>
+        <v>23037409</v>
       </c>
       <c r="G5">
-        <v>26392303</v>
+        <v>56055601</v>
       </c>
       <c r="H5">
-        <v>68049080</v>
+        <v>131051401</v>
       </c>
       <c r="I5">
-        <v>22481456</v>
+        <v>21271125</v>
       </c>
       <c r="J5">
-        <v>6446</v>
+        <v>6121</v>
       </c>
       <c r="K5">
-        <v>3479623</v>
+        <v>368</v>
       </c>
       <c r="L5">
-        <v>99862</v>
-      </c>
-      <c r="M5">
-        <v>27.9</v>
-      </c>
-      <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5">
-        <v>778319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>44347</v>
       </c>
       <c r="B6">
-        <v>162461</v>
+        <v>1058471</v>
       </c>
       <c r="C6">
-        <v>27519786</v>
+        <v>13344175</v>
       </c>
       <c r="D6">
-        <v>143.6</v>
+        <v>70</v>
       </c>
       <c r="E6">
-        <v>2960661</v>
+        <v>7408942</v>
       </c>
       <c r="F6">
-        <v>11957419</v>
+        <v>29300738</v>
       </c>
       <c r="G6">
-        <v>28746642</v>
+        <v>52919109</v>
       </c>
       <c r="H6">
-        <v>69427455</v>
+        <v>124197276</v>
       </c>
       <c r="I6">
-        <v>15898454</v>
+        <v>19868962</v>
       </c>
       <c r="J6">
-        <v>4536</v>
+        <v>5830</v>
       </c>
       <c r="K6">
-        <v>1587593</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L6">
-        <v>45403</v>
-      </c>
-      <c r="M6">
-        <v>172.5</v>
-      </c>
-      <c r="N6">
         <v>0</v>
       </c>
-      <c r="O6">
-        <v>666155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>44377</v>
       </c>
       <c r="B7">
-        <v>143154</v>
+        <v>1004959</v>
       </c>
       <c r="C7">
-        <v>15997009</v>
+        <v>22627392</v>
       </c>
       <c r="D7">
-        <v>88.8</v>
+        <v>127</v>
       </c>
       <c r="E7">
-        <v>117492</v>
+        <v>99441</v>
       </c>
       <c r="F7">
-        <v>483869</v>
+        <v>381460</v>
       </c>
       <c r="G7">
-        <v>39159642</v>
+        <v>18670649</v>
       </c>
       <c r="H7">
-        <v>97973044</v>
+        <v>48020721</v>
       </c>
       <c r="I7">
-        <v>26894991</v>
+        <v>26050030</v>
       </c>
       <c r="J7">
-        <v>7618</v>
+        <v>6888</v>
       </c>
       <c r="K7">
-        <v>1970296</v>
+        <v>104.3</v>
       </c>
       <c r="L7">
-        <v>54210</v>
-      </c>
-      <c r="M7">
-        <v>291</v>
-      </c>
-      <c r="N7">
         <v>0</v>
       </c>
-      <c r="O7">
-        <v>619391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>44408</v>
       </c>
       <c r="B8">
-        <v>142518</v>
+        <v>842405</v>
       </c>
       <c r="C8">
-        <v>23126578</v>
+        <v>25049369</v>
       </c>
       <c r="D8">
-        <v>124.7</v>
+        <v>134.6</v>
       </c>
       <c r="E8">
-        <v>79422</v>
+        <v>9776946</v>
       </c>
       <c r="F8">
-        <v>310542</v>
+        <v>39252370</v>
       </c>
       <c r="G8">
-        <v>47424692</v>
+        <v>34237530</v>
       </c>
       <c r="H8">
-        <v>112022663</v>
+        <v>83063144</v>
       </c>
       <c r="I8">
-        <v>20834579</v>
+        <v>8005919</v>
       </c>
       <c r="J8">
-        <v>6098</v>
+        <v>2267</v>
       </c>
       <c r="K8">
-        <v>4322443</v>
+        <v>69.3</v>
       </c>
       <c r="L8">
-        <v>121992</v>
-      </c>
-      <c r="M8">
-        <v>191.4</v>
-      </c>
-      <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8">
-        <v>534483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>44439</v>
       </c>
       <c r="B9">
-        <v>149779</v>
+        <v>897396</v>
       </c>
       <c r="C9">
-        <v>7041218</v>
+        <v>15796079</v>
       </c>
       <c r="D9">
-        <v>38.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E9">
-        <v>75790</v>
+        <v>11477222</v>
       </c>
       <c r="F9">
-        <v>326652</v>
+        <v>45628941</v>
       </c>
       <c r="G9">
-        <v>73606046</v>
+        <v>33354938</v>
       </c>
       <c r="H9">
-        <v>177100855</v>
+        <v>80608893</v>
       </c>
       <c r="I9">
-        <v>22372011</v>
+        <v>12781072</v>
       </c>
       <c r="J9">
-        <v>6199</v>
+        <v>3514</v>
       </c>
       <c r="K9">
-        <v>2939768</v>
+        <v>343.4</v>
       </c>
       <c r="L9">
-        <v>83134</v>
-      </c>
-      <c r="M9">
-        <v>174.4</v>
-      </c>
-      <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9">
-        <v>550638</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <v>44469</v>
       </c>
       <c r="B10">
-        <v>134101</v>
+        <v>896981</v>
       </c>
       <c r="C10">
-        <v>17647214</v>
+        <v>13216232</v>
       </c>
       <c r="D10">
-        <v>92.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="E10">
-        <v>2102838</v>
+        <v>5032553</v>
       </c>
       <c r="F10">
-        <v>8475972</v>
+        <v>19317126</v>
       </c>
       <c r="G10">
-        <v>22681822</v>
+        <v>54433084</v>
       </c>
       <c r="H10">
-        <v>56294110</v>
+        <v>132857203</v>
       </c>
       <c r="I10">
-        <v>605255</v>
+        <v>13686631</v>
       </c>
       <c r="J10">
-        <v>159</v>
+        <v>3790</v>
       </c>
       <c r="K10">
-        <v>2923206</v>
+        <v>334</v>
       </c>
       <c r="L10">
-        <v>80518</v>
-      </c>
-      <c r="M10">
-        <v>379.1</v>
-      </c>
-      <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10">
-        <v>630790</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <v>44500</v>
       </c>
       <c r="B11">
-        <v>180675</v>
+        <v>886590</v>
       </c>
       <c r="C11">
-        <v>17997836</v>
+        <v>15137218</v>
       </c>
       <c r="D11">
-        <v>104.7</v>
+        <v>85.5</v>
       </c>
       <c r="E11">
-        <v>3644882</v>
+        <v>201244</v>
       </c>
       <c r="F11">
-        <v>13358939</v>
+        <v>771164</v>
       </c>
       <c r="G11">
-        <v>34397657</v>
+        <v>34200560</v>
       </c>
       <c r="H11">
-        <v>82117570</v>
+        <v>83283612</v>
       </c>
       <c r="I11">
-        <v>18240035</v>
+        <v>13977217</v>
       </c>
       <c r="J11">
-        <v>4941</v>
+        <v>3651</v>
       </c>
       <c r="K11">
-        <v>2076249</v>
+        <v>330.8</v>
       </c>
       <c r="L11">
-        <v>55503</v>
-      </c>
-      <c r="M11">
-        <v>190.6</v>
-      </c>
-      <c r="N11">
-        <v>0.12</v>
-      </c>
-      <c r="O11">
-        <v>771152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <v>44530</v>
       </c>
       <c r="B12">
-        <v>207396</v>
+        <v>1140317</v>
       </c>
       <c r="C12">
-        <v>18888723</v>
+        <v>14767606</v>
       </c>
       <c r="D12">
-        <v>97.7</v>
+        <v>81</v>
       </c>
       <c r="E12">
-        <v>4385285</v>
+        <v>7505740</v>
       </c>
       <c r="F12">
-        <v>17629286</v>
+        <v>28419982</v>
       </c>
       <c r="G12">
-        <v>24194230</v>
+        <v>41484927</v>
       </c>
       <c r="H12">
-        <v>60099327</v>
+        <v>96374355</v>
       </c>
       <c r="I12">
-        <v>29512731</v>
+        <v>23437241</v>
       </c>
       <c r="J12">
-        <v>7840</v>
+        <v>6465</v>
       </c>
       <c r="K12">
-        <v>3841519</v>
+        <v>50.4</v>
       </c>
       <c r="L12">
-        <v>102608</v>
-      </c>
-      <c r="M12">
-        <v>220.7</v>
-      </c>
-      <c r="N12">
-        <v>5.86</v>
-      </c>
-      <c r="O12">
-        <v>862833</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <v>44561</v>
       </c>
       <c r="B13">
-        <v>214952</v>
+        <v>1395764</v>
       </c>
       <c r="C13">
-        <v>35749247</v>
+        <v>23669579</v>
       </c>
       <c r="D13">
-        <v>194.1</v>
+        <v>123</v>
       </c>
       <c r="E13">
-        <v>1453040</v>
+        <v>8868024</v>
       </c>
       <c r="F13">
-        <v>5531362</v>
+        <v>32762745</v>
       </c>
       <c r="G13">
-        <v>777414</v>
+        <v>59852953</v>
       </c>
       <c r="H13">
-        <v>1896369</v>
+        <v>139708244</v>
       </c>
       <c r="I13">
-        <v>7885031</v>
+        <v>35242781</v>
       </c>
       <c r="J13">
-        <v>2225</v>
+        <v>9616</v>
       </c>
       <c r="K13">
-        <v>2884005</v>
+        <v>398.4</v>
       </c>
       <c r="L13">
-        <v>79829</v>
-      </c>
-      <c r="M13">
-        <v>218.5</v>
-      </c>
-      <c r="N13">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="O13">
-        <v>954411</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1">
         <v>44592</v>
       </c>
       <c r="B14">
-        <v>226017</v>
+        <v>1177568</v>
       </c>
       <c r="C14">
-        <v>15173576</v>
+        <v>23917267</v>
       </c>
       <c r="D14">
-        <v>80.5</v>
+        <v>124.6</v>
       </c>
       <c r="E14">
-        <v>3739645</v>
+        <v>8386786</v>
       </c>
       <c r="F14">
-        <v>14382354</v>
+        <v>31608793</v>
       </c>
       <c r="G14">
-        <v>1267210</v>
+        <v>30276465</v>
       </c>
       <c r="H14">
-        <v>3026925</v>
+        <v>71238482</v>
       </c>
       <c r="I14">
-        <v>12602614</v>
+        <v>12805753</v>
       </c>
       <c r="J14">
-        <v>3553</v>
+        <v>3557</v>
       </c>
       <c r="K14">
-        <v>3783857</v>
+        <v>55.5</v>
       </c>
       <c r="L14">
-        <v>101548</v>
-      </c>
-      <c r="M14">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="N14">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="O14">
-        <v>917606</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1">
         <v>44620</v>
       </c>
       <c r="B15">
-        <v>209006</v>
+        <v>1090579</v>
       </c>
       <c r="C15">
-        <v>39685404</v>
+        <v>8033476</v>
       </c>
       <c r="D15">
-        <v>207.3</v>
+        <v>43.9</v>
       </c>
       <c r="E15">
-        <v>7903670</v>
+        <v>8329089</v>
       </c>
       <c r="F15">
-        <v>29885736</v>
+        <v>32251256</v>
       </c>
       <c r="G15">
-        <v>30652393</v>
+        <v>56207344</v>
       </c>
       <c r="H15">
-        <v>70981842</v>
+        <v>132825453</v>
       </c>
       <c r="I15">
-        <v>7199532</v>
+        <v>12772539</v>
       </c>
       <c r="J15">
-        <v>1951</v>
+        <v>3455</v>
       </c>
       <c r="K15">
-        <v>2146333</v>
+        <v>104.7</v>
       </c>
       <c r="L15">
-        <v>59154</v>
-      </c>
-      <c r="M15">
-        <v>226.5</v>
-      </c>
-      <c r="N15">
-        <v>7.18</v>
-      </c>
-      <c r="O15">
-        <v>940461</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1">
         <v>44651</v>
       </c>
       <c r="B16">
-        <v>218092</v>
+        <v>1077450</v>
       </c>
       <c r="C16">
-        <v>23836327</v>
+        <v>22084677</v>
       </c>
       <c r="D16">
-        <v>127.4</v>
+        <v>118.4</v>
       </c>
       <c r="E16">
-        <v>6195058</v>
+        <v>8045114</v>
       </c>
       <c r="F16">
-        <v>24307143</v>
+        <v>30608922</v>
       </c>
       <c r="G16">
-        <v>35039433</v>
+        <v>35527721</v>
       </c>
       <c r="H16">
-        <v>75347339</v>
+        <v>82171553</v>
       </c>
       <c r="I16">
-        <v>26325388</v>
+        <v>17592196</v>
       </c>
       <c r="J16">
-        <v>7076</v>
+        <v>4528</v>
       </c>
       <c r="K16">
-        <v>4235142</v>
+        <v>269.5</v>
       </c>
       <c r="L16">
-        <v>118498</v>
-      </c>
-      <c r="M16">
-        <v>68.3</v>
-      </c>
-      <c r="N16">
-        <v>2.18</v>
-      </c>
-      <c r="O16">
-        <v>809232</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <v>44681</v>
       </c>
       <c r="B17">
-        <v>189120</v>
+        <v>956666</v>
       </c>
       <c r="C17">
-        <v>45496143</v>
+        <v>22405328</v>
       </c>
       <c r="D17">
-        <v>233.1</v>
+        <v>119.1</v>
       </c>
       <c r="E17">
-        <v>8157872</v>
+        <v>8570386</v>
       </c>
       <c r="F17">
-        <v>29633019</v>
+        <v>33919343</v>
       </c>
       <c r="G17">
-        <v>42855535</v>
+        <v>58799188</v>
       </c>
       <c r="H17">
-        <v>98881220</v>
+        <v>143245499</v>
       </c>
       <c r="I17">
-        <v>14060635</v>
+        <v>9193174</v>
       </c>
       <c r="J17">
-        <v>3818</v>
+        <v>2566</v>
       </c>
       <c r="K17">
-        <v>1787697</v>
+        <v>140.2</v>
       </c>
       <c r="L17">
-        <v>47344</v>
-      </c>
-      <c r="M17">
-        <v>167.5</v>
-      </c>
-      <c r="N17">
         <v>0</v>
       </c>
-      <c r="O17">
-        <v>790230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <v>44712</v>
       </c>
       <c r="B18">
-        <v>165227</v>
+        <v>855047</v>
       </c>
       <c r="C18">
-        <v>31064439</v>
+        <v>27726375</v>
       </c>
       <c r="D18">
-        <v>165.2</v>
+        <v>147.1</v>
       </c>
       <c r="E18">
-        <v>527386</v>
+        <v>10177631</v>
       </c>
       <c r="F18">
-        <v>2051598</v>
+        <v>38234669</v>
       </c>
       <c r="G18">
-        <v>30320550</v>
+        <v>35940348</v>
       </c>
       <c r="H18">
-        <v>72739903</v>
+        <v>83765859</v>
       </c>
       <c r="I18">
-        <v>23860739</v>
+        <v>6516390</v>
       </c>
       <c r="J18">
-        <v>6467</v>
+        <v>1787</v>
       </c>
       <c r="K18">
-        <v>3307825</v>
+        <v>318.7</v>
       </c>
       <c r="L18">
-        <v>88939</v>
-      </c>
-      <c r="M18">
-        <v>202.9</v>
-      </c>
-      <c r="N18">
         <v>0</v>
       </c>
-      <c r="O18">
-        <v>642331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <v>44742</v>
       </c>
       <c r="B19">
-        <v>155774</v>
+        <v>961540</v>
       </c>
       <c r="C19">
-        <v>14297123</v>
+        <v>9410294</v>
       </c>
       <c r="D19">
-        <v>79.5</v>
+        <v>48.6</v>
       </c>
       <c r="E19">
-        <v>2470121</v>
+        <v>10732173</v>
       </c>
       <c r="F19">
-        <v>9404392</v>
+        <v>40355993</v>
       </c>
       <c r="G19">
-        <v>76514313</v>
+        <v>34242354</v>
       </c>
       <c r="H19">
-        <v>194525906</v>
+        <v>80513452</v>
       </c>
       <c r="I19">
-        <v>27904660</v>
+        <v>18258344</v>
       </c>
       <c r="J19">
-        <v>7463</v>
+        <v>5058</v>
       </c>
       <c r="K19">
-        <v>2829488</v>
+        <v>172.6</v>
       </c>
       <c r="L19">
-        <v>79884</v>
-      </c>
-      <c r="M19">
-        <v>200.4</v>
-      </c>
-      <c r="N19">
         <v>0</v>
       </c>
-      <c r="O19">
-        <v>605020</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <v>44773</v>
       </c>
       <c r="B20">
-        <v>142445</v>
+        <v>945136</v>
       </c>
       <c r="C20">
-        <v>24260824</v>
+        <v>23570227</v>
       </c>
       <c r="D20">
-        <v>127.5</v>
+        <v>125.7</v>
       </c>
       <c r="E20">
-        <v>1679984</v>
+        <v>4832320</v>
       </c>
       <c r="F20">
-        <v>6327523</v>
+        <v>18003657</v>
       </c>
       <c r="G20">
-        <v>29804555</v>
+        <v>21948232</v>
       </c>
       <c r="H20">
-        <v>70097100</v>
+        <v>49455673</v>
       </c>
       <c r="I20">
-        <v>23894695</v>
+        <v>21550292</v>
       </c>
       <c r="J20">
-        <v>6452</v>
+        <v>5762</v>
       </c>
       <c r="K20">
-        <v>3108211</v>
+        <v>344.2</v>
       </c>
       <c r="L20">
-        <v>87474</v>
-      </c>
-      <c r="M20">
-        <v>321.5</v>
-      </c>
-      <c r="N20">
         <v>0</v>
       </c>
-      <c r="O20">
-        <v>558543</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <v>44804</v>
       </c>
       <c r="B21">
-        <v>141750</v>
+        <v>790217</v>
       </c>
       <c r="C21">
-        <v>2149498</v>
+        <v>14893056</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E21">
-        <v>5304193</v>
+        <v>7929469</v>
       </c>
       <c r="F21">
-        <v>20799152</v>
+        <v>28610100</v>
       </c>
       <c r="G21">
-        <v>760480</v>
+        <v>24335596</v>
       </c>
       <c r="H21">
-        <v>1846314</v>
+        <v>56204639</v>
       </c>
       <c r="I21">
-        <v>6951597</v>
+        <v>5794313</v>
       </c>
       <c r="J21">
-        <v>1894</v>
+        <v>1530</v>
       </c>
       <c r="K21">
-        <v>5637364</v>
+        <v>94.5</v>
       </c>
       <c r="L21">
-        <v>152143</v>
-      </c>
-      <c r="M21">
-        <v>116.4</v>
-      </c>
-      <c r="N21">
         <v>0</v>
       </c>
-      <c r="O21">
-        <v>571885</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1">
         <v>44834</v>
       </c>
       <c r="B22">
-        <v>168786</v>
+        <v>829040</v>
       </c>
       <c r="C22">
-        <v>225345</v>
+        <v>16461895</v>
       </c>
       <c r="D22">
-        <v>1.2</v>
+        <v>82.3</v>
       </c>
       <c r="E22">
-        <v>4996657</v>
+        <v>5626126</v>
       </c>
       <c r="F22">
-        <v>17954922</v>
+        <v>21233382</v>
       </c>
       <c r="G22">
-        <v>88545269</v>
+        <v>34921735</v>
       </c>
       <c r="H22">
-        <v>203884306</v>
+        <v>89887841</v>
       </c>
       <c r="I22">
-        <v>31242954</v>
+        <v>10688201</v>
       </c>
       <c r="J22">
-        <v>8255</v>
+        <v>2894</v>
       </c>
       <c r="K22">
-        <v>1159227</v>
+        <v>219.6</v>
       </c>
       <c r="L22">
-        <v>29387</v>
-      </c>
-      <c r="M22">
-        <v>131.7</v>
-      </c>
-      <c r="N22">
         <v>0</v>
       </c>
-      <c r="O22">
-        <v>673214</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1">
         <v>44865</v>
       </c>
       <c r="B23">
-        <v>190380</v>
+        <v>930965</v>
       </c>
       <c r="C23">
-        <v>29954456</v>
+        <v>20263161</v>
       </c>
       <c r="D23">
-        <v>153.4</v>
+        <v>102.7</v>
       </c>
       <c r="E23">
-        <v>614015</v>
+        <v>4409552</v>
       </c>
       <c r="F23">
-        <v>2274527</v>
+        <v>16178074</v>
       </c>
       <c r="G23">
-        <v>23299214</v>
+        <v>42890495</v>
       </c>
       <c r="H23">
-        <v>50250926</v>
+        <v>97700135</v>
       </c>
       <c r="I23">
-        <v>15324728</v>
+        <v>14378383</v>
       </c>
       <c r="J23">
-        <v>4156</v>
+        <v>3886</v>
       </c>
       <c r="K23">
-        <v>4868215</v>
+        <v>63.9</v>
       </c>
       <c r="L23">
-        <v>128674</v>
-      </c>
-      <c r="M23">
-        <v>109.8</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>738577</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1">
         <v>44895</v>
       </c>
       <c r="B24">
-        <v>207571</v>
+        <v>940814</v>
       </c>
       <c r="C24">
-        <v>27106260</v>
+        <v>837225</v>
       </c>
       <c r="D24">
-        <v>142.6</v>
+        <v>4</v>
       </c>
       <c r="E24">
-        <v>3925334</v>
+        <v>15328017</v>
       </c>
       <c r="F24">
-        <v>14657896</v>
+        <v>54736294</v>
       </c>
       <c r="G24">
-        <v>66075484</v>
+        <v>46752701</v>
       </c>
       <c r="H24">
-        <v>151533713</v>
+        <v>109067177</v>
       </c>
       <c r="I24">
-        <v>9366593</v>
+        <v>101213</v>
       </c>
       <c r="J24">
-        <v>2562</v>
+        <v>27</v>
       </c>
       <c r="K24">
-        <v>3918583</v>
+        <v>157.4</v>
       </c>
       <c r="L24">
-        <v>103252</v>
-      </c>
-      <c r="M24">
-        <v>222</v>
-      </c>
-      <c r="N24">
-        <v>12.26</v>
-      </c>
-      <c r="O24">
-        <v>901778</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1">
         <v>44926</v>
       </c>
       <c r="B25">
-        <v>225883</v>
+        <v>1269946</v>
       </c>
       <c r="C25">
-        <v>16480380</v>
+        <v>36333495</v>
       </c>
       <c r="D25">
-        <v>83.2</v>
+        <v>187.5</v>
       </c>
       <c r="E25">
-        <v>5361921</v>
+        <v>9626837</v>
       </c>
       <c r="F25">
-        <v>19103243</v>
+        <v>36260798</v>
       </c>
       <c r="G25">
-        <v>2040056</v>
+        <v>889591</v>
       </c>
       <c r="H25">
-        <v>4534769</v>
+        <v>1966297</v>
       </c>
       <c r="I25">
-        <v>19921286</v>
+        <v>30347624</v>
       </c>
       <c r="J25">
-        <v>5133</v>
+        <v>7957</v>
       </c>
       <c r="K25">
-        <v>1191998</v>
+        <v>113</v>
       </c>
       <c r="L25">
-        <v>32844</v>
-      </c>
-      <c r="M25">
-        <v>151.2</v>
-      </c>
-      <c r="N25">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="O25">
-        <v>963631</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1">
         <v>44957</v>
       </c>
       <c r="B26">
-        <v>220339</v>
+        <v>1251873</v>
       </c>
       <c r="C26">
-        <v>347180</v>
+        <v>16474954</v>
       </c>
       <c r="D26">
-        <v>1.8</v>
+        <v>83.7</v>
       </c>
       <c r="E26">
-        <v>36765</v>
+        <v>11268245</v>
       </c>
       <c r="F26">
-        <v>141688</v>
+        <v>39432611</v>
       </c>
       <c r="G26">
-        <v>53017446</v>
+        <v>62391592</v>
       </c>
       <c r="H26">
-        <v>119425561</v>
+        <v>146415657</v>
       </c>
       <c r="I26">
-        <v>19716251</v>
+        <v>19667175</v>
       </c>
       <c r="J26">
-        <v>5338</v>
+        <v>5144</v>
       </c>
       <c r="K26">
-        <v>4552507</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L26">
-        <v>117531</v>
-      </c>
-      <c r="M26">
-        <v>234.8</v>
-      </c>
-      <c r="N26">
-        <v>7.69</v>
-      </c>
-      <c r="O26">
-        <v>931039</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1">
         <v>44985</v>
       </c>
       <c r="B27">
-        <v>222245</v>
+        <v>1177561</v>
       </c>
       <c r="C27">
-        <v>14878905</v>
+        <v>35963214</v>
       </c>
       <c r="D27">
-        <v>72.5</v>
+        <v>182.6</v>
       </c>
       <c r="E27">
-        <v>6873701</v>
+        <v>8307741</v>
       </c>
       <c r="F27">
-        <v>24071958</v>
+        <v>31319706</v>
       </c>
       <c r="G27">
-        <v>1561827</v>
+        <v>43436438</v>
       </c>
       <c r="H27">
-        <v>3365599</v>
+        <v>96929517</v>
       </c>
       <c r="I27">
-        <v>17430815</v>
+        <v>18753655</v>
       </c>
       <c r="J27">
-        <v>4457</v>
+        <v>4649</v>
       </c>
       <c r="K27">
-        <v>5666333</v>
+        <v>118.4</v>
       </c>
       <c r="L27">
-        <v>142188</v>
-      </c>
-      <c r="M27">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="N27">
-        <v>4.46</v>
-      </c>
-      <c r="O27">
-        <v>946518</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="1">
         <v>45016</v>
       </c>
       <c r="B28">
-        <v>214704</v>
+        <v>1074621</v>
       </c>
       <c r="C28">
-        <v>43768702</v>
+        <v>14732803</v>
       </c>
       <c r="D28">
-        <v>225.3</v>
+        <v>69.7</v>
       </c>
       <c r="E28">
-        <v>2227628</v>
+        <v>6184392</v>
       </c>
       <c r="F28">
-        <v>8040038</v>
+        <v>22196525</v>
       </c>
       <c r="G28">
-        <v>52084404</v>
+        <v>26434051</v>
       </c>
       <c r="H28">
-        <v>113570010</v>
+        <v>59540959</v>
       </c>
       <c r="I28">
-        <v>16370044</v>
+        <v>17194311</v>
       </c>
       <c r="J28">
-        <v>4269</v>
+        <v>4389</v>
       </c>
       <c r="K28">
-        <v>2835812</v>
+        <v>71</v>
       </c>
       <c r="L28">
-        <v>74116</v>
-      </c>
-      <c r="M28">
-        <v>148</v>
-      </c>
-      <c r="N28">
-        <v>2.85</v>
-      </c>
-      <c r="O28">
-        <v>894731</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="1">
         <v>45046</v>
       </c>
       <c r="B29">
-        <v>188034</v>
+        <v>820287</v>
       </c>
       <c r="C29">
-        <v>23694596</v>
+        <v>8457375</v>
       </c>
       <c r="D29">
-        <v>122.5</v>
+        <v>43.3</v>
       </c>
       <c r="E29">
-        <v>105719</v>
+        <v>208362</v>
       </c>
       <c r="F29">
-        <v>391634</v>
+        <v>748360</v>
       </c>
       <c r="G29">
-        <v>42603902</v>
+        <v>27212819</v>
       </c>
       <c r="H29">
-        <v>93396975</v>
+        <v>62607911</v>
       </c>
       <c r="I29">
-        <v>45946393</v>
+        <v>6960783</v>
       </c>
       <c r="J29">
-        <v>12094</v>
+        <v>1867</v>
       </c>
       <c r="K29">
-        <v>3414892</v>
+        <v>91.2</v>
       </c>
       <c r="L29">
-        <v>84779</v>
-      </c>
-      <c r="M29">
-        <v>217.8</v>
-      </c>
-      <c r="N29">
         <v>0</v>
       </c>
-      <c r="O29">
-        <v>782720</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1">
         <v>45077</v>
       </c>
       <c r="B30">
-        <v>165540</v>
+        <v>847560</v>
       </c>
       <c r="C30">
-        <v>34224837</v>
+        <v>18095173</v>
       </c>
       <c r="D30">
-        <v>160.5</v>
+        <v>86.3</v>
       </c>
       <c r="E30">
-        <v>3783814</v>
+        <v>4901535</v>
       </c>
       <c r="F30">
-        <v>13207516</v>
+        <v>17598270</v>
       </c>
       <c r="G30">
-        <v>34977889</v>
+        <v>22833027</v>
       </c>
       <c r="H30">
-        <v>78892137</v>
+        <v>52179546</v>
       </c>
       <c r="I30">
-        <v>11510920</v>
+        <v>16506408</v>
       </c>
       <c r="J30">
-        <v>2897</v>
+        <v>4265</v>
       </c>
       <c r="K30">
-        <v>3454266</v>
+        <v>256.2</v>
       </c>
       <c r="L30">
-        <v>90680</v>
-      </c>
-      <c r="M30">
-        <v>220.8</v>
-      </c>
-      <c r="N30">
         <v>0</v>
       </c>
-      <c r="O30">
-        <v>668451</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="1">
         <v>45107</v>
       </c>
       <c r="B31">
-        <v>123163</v>
+        <v>803900</v>
       </c>
       <c r="C31">
-        <v>38464249</v>
+        <v>21260723</v>
       </c>
       <c r="D31">
-        <v>182.9</v>
+        <v>105.2</v>
       </c>
       <c r="E31">
-        <v>387548</v>
+        <v>8269036</v>
       </c>
       <c r="F31">
-        <v>1388312</v>
+        <v>29298062</v>
       </c>
       <c r="G31">
-        <v>33637343</v>
+        <v>54785896</v>
       </c>
       <c r="H31">
-        <v>75707615</v>
+        <v>118940850</v>
       </c>
       <c r="I31">
-        <v>181654</v>
+        <v>11209465</v>
       </c>
       <c r="J31">
-        <v>47</v>
+        <v>2741</v>
       </c>
       <c r="K31">
-        <v>4340919</v>
+        <v>318.7</v>
       </c>
       <c r="L31">
-        <v>114894</v>
-      </c>
-      <c r="M31">
-        <v>283.2</v>
-      </c>
-      <c r="N31">
         <v>0</v>
       </c>
-      <c r="O31">
-        <v>609336</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="1">
         <v>45138</v>
       </c>
       <c r="B32">
-        <v>122131</v>
+        <v>949795</v>
       </c>
       <c r="C32">
-        <v>8769652</v>
+        <v>11908583</v>
       </c>
       <c r="D32">
-        <v>41.9</v>
+        <v>58.8</v>
       </c>
       <c r="E32">
-        <v>45091</v>
+        <v>9792485</v>
       </c>
       <c r="F32">
-        <v>158594</v>
+        <v>35994043</v>
       </c>
       <c r="G32">
-        <v>31191070</v>
+        <v>68358420</v>
       </c>
       <c r="H32">
-        <v>72001944</v>
+        <v>144412149</v>
       </c>
       <c r="I32">
-        <v>15752570</v>
+        <v>20833720</v>
       </c>
       <c r="J32">
-        <v>3923</v>
+        <v>5329</v>
       </c>
       <c r="K32">
-        <v>3789419</v>
+        <v>85.8</v>
       </c>
       <c r="L32">
-        <v>96554</v>
-      </c>
-      <c r="M32">
-        <v>317.6</v>
-      </c>
-      <c r="N32">
         <v>0</v>
       </c>
-      <c r="O32">
-        <v>578742</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="1">
         <v>45169</v>
       </c>
       <c r="B33">
-        <v>149361</v>
+        <v>953778</v>
       </c>
       <c r="C33">
-        <v>34066662</v>
+        <v>28691858</v>
       </c>
       <c r="D33">
-        <v>164</v>
+        <v>146.3</v>
       </c>
       <c r="E33">
-        <v>7693574</v>
+        <v>5990470</v>
       </c>
       <c r="F33">
-        <v>26999466</v>
+        <v>21403617</v>
       </c>
       <c r="G33">
-        <v>66343091</v>
+        <v>33318369</v>
       </c>
       <c r="H33">
-        <v>154287205</v>
+        <v>73818889</v>
       </c>
       <c r="I33">
-        <v>16179170</v>
+        <v>20201562</v>
       </c>
       <c r="J33">
-        <v>3919</v>
+        <v>5151</v>
       </c>
       <c r="K33">
-        <v>2404038</v>
+        <v>146.4</v>
       </c>
       <c r="L33">
-        <v>63195</v>
-      </c>
-      <c r="M33">
-        <v>157.4</v>
-      </c>
-      <c r="N33">
         <v>0</v>
       </c>
-      <c r="O33">
-        <v>573045</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="1">
         <v>45199</v>
       </c>
       <c r="B34">
-        <v>168933</v>
+        <v>917061</v>
       </c>
       <c r="C34">
-        <v>17652386</v>
+        <v>31308641</v>
       </c>
       <c r="D34">
-        <v>82.90000000000001</v>
+        <v>164.6</v>
       </c>
       <c r="E34">
-        <v>6725080</v>
+        <v>6056845</v>
       </c>
       <c r="F34">
-        <v>23620468</v>
+        <v>22379819</v>
       </c>
       <c r="G34">
-        <v>24938858</v>
+        <v>59582686</v>
       </c>
       <c r="H34">
-        <v>55661332</v>
+        <v>134392348</v>
       </c>
       <c r="I34">
-        <v>35116412</v>
+        <v>14332272</v>
       </c>
       <c r="J34">
-        <v>9209</v>
+        <v>3623</v>
       </c>
       <c r="K34">
-        <v>1693288</v>
+        <v>253.3</v>
       </c>
       <c r="L34">
-        <v>42984</v>
-      </c>
-      <c r="M34">
-        <v>198.8</v>
-      </c>
-      <c r="N34">
         <v>0</v>
       </c>
-      <c r="O34">
-        <v>689381</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="1">
         <v>45230</v>
       </c>
       <c r="B35">
-        <v>170814</v>
+        <v>968383</v>
       </c>
       <c r="C35">
-        <v>26112491</v>
+        <v>17770707</v>
       </c>
       <c r="D35">
-        <v>128.4</v>
+        <v>85.3</v>
       </c>
       <c r="E35">
-        <v>5068018</v>
+        <v>8432198</v>
       </c>
       <c r="F35">
-        <v>17850120</v>
+        <v>29189548</v>
       </c>
       <c r="G35">
-        <v>1009180</v>
+        <v>24055367</v>
       </c>
       <c r="H35">
-        <v>2268753</v>
+        <v>52389461</v>
       </c>
       <c r="I35">
-        <v>168058</v>
+        <v>14461448</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>3696</v>
       </c>
       <c r="K35">
-        <v>5980618</v>
+        <v>171.8</v>
       </c>
       <c r="L35">
-        <v>153656</v>
-      </c>
-      <c r="M35">
-        <v>145.5</v>
-      </c>
-      <c r="N35">
         <v>0</v>
       </c>
-      <c r="O35">
-        <v>747190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="1">
         <v>45260</v>
       </c>
       <c r="B36">
-        <v>204281</v>
+        <v>1201431</v>
       </c>
       <c r="C36">
-        <v>1012954</v>
+        <v>22670668</v>
       </c>
       <c r="D36">
-        <v>4.9</v>
+        <v>117.2</v>
       </c>
       <c r="E36">
-        <v>201601</v>
+        <v>12496754</v>
       </c>
       <c r="F36">
-        <v>723414</v>
+        <v>42298023</v>
       </c>
       <c r="G36">
-        <v>73433830</v>
+        <v>1053986</v>
       </c>
       <c r="H36">
-        <v>154791418</v>
+        <v>2378663</v>
       </c>
       <c r="I36">
-        <v>11524064</v>
+        <v>26306903</v>
       </c>
       <c r="J36">
-        <v>2843</v>
+        <v>6857</v>
       </c>
       <c r="K36">
-        <v>4290658</v>
+        <v>37.3</v>
       </c>
       <c r="L36">
-        <v>103610</v>
-      </c>
-      <c r="M36">
-        <v>75</v>
-      </c>
-      <c r="N36">
-        <v>5.18</v>
-      </c>
-      <c r="O36">
-        <v>916301</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="1">
         <v>45291</v>
       </c>
       <c r="B37">
-        <v>209423</v>
+        <v>1017663</v>
       </c>
       <c r="C37">
-        <v>44270312</v>
+        <v>58511876</v>
       </c>
       <c r="D37">
-        <v>213.5</v>
+        <v>278.9</v>
       </c>
       <c r="E37">
-        <v>4488924</v>
+        <v>154988</v>
       </c>
       <c r="F37">
-        <v>15799634</v>
+        <v>536716</v>
       </c>
       <c r="G37">
-        <v>42757091</v>
+        <v>57985608</v>
       </c>
       <c r="H37">
-        <v>90875412</v>
+        <v>128459081</v>
       </c>
       <c r="I37">
-        <v>234896</v>
+        <v>11189456</v>
       </c>
       <c r="J37">
-        <v>59</v>
+        <v>2871</v>
       </c>
       <c r="K37">
-        <v>2737812</v>
+        <v>170.5</v>
       </c>
       <c r="L37">
-        <v>68365</v>
-      </c>
-      <c r="M37">
-        <v>86.2</v>
-      </c>
-      <c r="N37">
-        <v>7.6</v>
-      </c>
-      <c r="O37">
-        <v>1021387</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="1">
         <v>45322</v>
       </c>
       <c r="B38">
-        <v>230797</v>
+        <v>1303786</v>
       </c>
       <c r="C38">
-        <v>47533494</v>
+        <v>14988278</v>
       </c>
       <c r="D38">
-        <v>222.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E38">
-        <v>2787894</v>
+        <v>22504469</v>
       </c>
       <c r="F38">
-        <v>9480382</v>
+        <v>77008249</v>
       </c>
       <c r="G38">
-        <v>39888202</v>
+        <v>62224047</v>
       </c>
       <c r="H38">
-        <v>84687270</v>
+        <v>138155102</v>
       </c>
       <c r="I38">
-        <v>17797541</v>
+        <v>22052338</v>
       </c>
       <c r="J38">
-        <v>4372</v>
+        <v>5573</v>
       </c>
       <c r="K38">
-        <v>6919037</v>
+        <v>156.9</v>
       </c>
       <c r="L38">
-        <v>164219</v>
-      </c>
-      <c r="M38">
-        <v>109</v>
-      </c>
-      <c r="N38">
-        <v>4.69</v>
-      </c>
-      <c r="O38">
-        <v>962368</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="1">
         <v>45351</v>
       </c>
       <c r="B39">
-        <v>213175</v>
+        <v>1423359</v>
       </c>
       <c r="C39">
-        <v>361221</v>
+        <v>29355932</v>
       </c>
       <c r="D39">
-        <v>1.7</v>
+        <v>149.8</v>
       </c>
       <c r="E39">
-        <v>2260284</v>
+        <v>10730526</v>
       </c>
       <c r="F39">
-        <v>8028728</v>
+        <v>38398963</v>
       </c>
       <c r="G39">
-        <v>749864</v>
+        <v>59171138</v>
       </c>
       <c r="H39">
-        <v>1663069</v>
+        <v>130332530</v>
       </c>
       <c r="I39">
-        <v>16865602</v>
+        <v>34784164</v>
       </c>
       <c r="J39">
-        <v>4052</v>
+        <v>8423</v>
       </c>
       <c r="K39">
-        <v>2433080</v>
+        <v>98.7</v>
       </c>
       <c r="L39">
-        <v>61433</v>
-      </c>
-      <c r="M39">
-        <v>242</v>
-      </c>
-      <c r="N39">
-        <v>9.9</v>
-      </c>
-      <c r="O39">
-        <v>971419</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="1">
         <v>45382</v>
       </c>
       <c r="B40">
-        <v>207260</v>
+        <v>1076087</v>
       </c>
       <c r="C40">
-        <v>41020791</v>
+        <v>35691979</v>
       </c>
       <c r="D40">
-        <v>190.3</v>
+        <v>174.1</v>
       </c>
       <c r="E40">
-        <v>1921829</v>
+        <v>5360918</v>
       </c>
       <c r="F40">
-        <v>6922430</v>
+        <v>18725435</v>
       </c>
       <c r="G40">
-        <v>805999</v>
+        <v>59584446</v>
       </c>
       <c r="H40">
-        <v>1763193</v>
+        <v>128715991</v>
       </c>
       <c r="I40">
-        <v>20679833</v>
+        <v>13266132</v>
       </c>
       <c r="J40">
-        <v>5011</v>
+        <v>3209</v>
       </c>
       <c r="K40">
-        <v>5067437</v>
+        <v>103.6</v>
       </c>
       <c r="L40">
-        <v>126306</v>
-      </c>
-      <c r="M40">
-        <v>37.4</v>
-      </c>
-      <c r="N40">
-        <v>3.94</v>
-      </c>
-      <c r="O40">
-        <v>889473</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="1">
         <v>45412</v>
       </c>
       <c r="B41">
-        <v>184669</v>
+        <v>1015008</v>
       </c>
       <c r="C41">
-        <v>25306915</v>
+        <v>29526289</v>
       </c>
       <c r="D41">
-        <v>114.6</v>
+        <v>138.8</v>
       </c>
       <c r="E41">
-        <v>3171892</v>
+        <v>5196253</v>
       </c>
       <c r="F41">
-        <v>11338707</v>
+        <v>19219292</v>
       </c>
       <c r="G41">
-        <v>76360283</v>
+        <v>17511373</v>
       </c>
       <c r="H41">
-        <v>157155266</v>
+        <v>38372110</v>
       </c>
       <c r="I41">
-        <v>10218535</v>
+        <v>21138934</v>
       </c>
       <c r="J41">
-        <v>2546</v>
+        <v>5085</v>
       </c>
       <c r="K41">
-        <v>3048026</v>
+        <v>370.3</v>
       </c>
       <c r="L41">
-        <v>77490</v>
-      </c>
-      <c r="M41">
-        <v>124.5</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>768139</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" s="1">
         <v>45443</v>
       </c>
       <c r="B42">
-        <v>158776</v>
+        <v>874381</v>
       </c>
       <c r="C42">
-        <v>861758</v>
+        <v>32881749</v>
       </c>
       <c r="D42">
-        <v>4.1</v>
+        <v>155.3</v>
       </c>
       <c r="E42">
-        <v>3236050</v>
+        <v>6160934</v>
       </c>
       <c r="F42">
-        <v>10866546</v>
+        <v>21626914</v>
       </c>
       <c r="G42">
-        <v>36650822</v>
+        <v>879536</v>
       </c>
       <c r="H42">
-        <v>85166914</v>
+        <v>1910358</v>
       </c>
       <c r="I42">
-        <v>18099079</v>
+        <v>14892581</v>
       </c>
       <c r="J42">
-        <v>4505</v>
+        <v>3763</v>
       </c>
       <c r="K42">
-        <v>4508393</v>
+        <v>284.4</v>
       </c>
       <c r="L42">
-        <v>110693</v>
-      </c>
-      <c r="M42">
-        <v>202.7</v>
-      </c>
-      <c r="N42">
         <v>0</v>
       </c>
-      <c r="O42">
-        <v>651432</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="1">
         <v>45473</v>
       </c>
       <c r="B43">
-        <v>150724</v>
+        <v>915650</v>
       </c>
       <c r="C43">
-        <v>489331</v>
+        <v>35976598</v>
       </c>
       <c r="D43">
-        <v>2.3</v>
+        <v>167.4</v>
       </c>
       <c r="E43">
-        <v>6998278</v>
+        <v>8109294</v>
       </c>
       <c r="F43">
-        <v>24002073</v>
+        <v>28004926</v>
       </c>
       <c r="G43">
-        <v>35633146</v>
+        <v>45999731</v>
       </c>
       <c r="H43">
-        <v>76461305</v>
+        <v>99473505</v>
       </c>
       <c r="I43">
-        <v>46065202</v>
+        <v>18562608</v>
       </c>
       <c r="J43">
-        <v>12299</v>
+        <v>4708</v>
       </c>
       <c r="K43">
-        <v>607551</v>
+        <v>239.2</v>
       </c>
       <c r="L43">
-        <v>16702</v>
-      </c>
-      <c r="M43">
-        <v>139.9</v>
-      </c>
-      <c r="N43">
         <v>0</v>
       </c>
-      <c r="O43">
-        <v>648096</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="1">
         <v>45504</v>
       </c>
       <c r="B44">
-        <v>140344</v>
+        <v>802813</v>
       </c>
       <c r="C44">
-        <v>12372035</v>
+        <v>24481732</v>
       </c>
       <c r="D44">
-        <v>58.3</v>
+        <v>114.8</v>
       </c>
       <c r="E44">
-        <v>3185162</v>
+        <v>8337865</v>
       </c>
       <c r="F44">
-        <v>11211614</v>
+        <v>28498152</v>
       </c>
       <c r="G44">
-        <v>44370075</v>
+        <v>28215233</v>
       </c>
       <c r="H44">
-        <v>97100105</v>
+        <v>61505150</v>
       </c>
       <c r="I44">
-        <v>562622</v>
+        <v>9353655</v>
       </c>
       <c r="J44">
-        <v>133</v>
+        <v>2343</v>
       </c>
       <c r="K44">
-        <v>6278365</v>
+        <v>164.9</v>
       </c>
       <c r="L44">
-        <v>155913</v>
-      </c>
-      <c r="M44">
-        <v>88</v>
-      </c>
-      <c r="N44">
         <v>0</v>
       </c>
-      <c r="O44">
-        <v>628917</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="1">
         <v>45535</v>
       </c>
       <c r="B45">
-        <v>141415</v>
+        <v>1021665</v>
       </c>
       <c r="C45">
-        <v>12537094</v>
+        <v>34434451</v>
       </c>
       <c r="D45">
-        <v>63.5</v>
+        <v>166</v>
       </c>
       <c r="E45">
-        <v>4656834</v>
+        <v>10351683</v>
       </c>
       <c r="F45">
-        <v>15562116</v>
+        <v>36796012</v>
       </c>
       <c r="G45">
-        <v>685153</v>
+        <v>45275003</v>
       </c>
       <c r="H45">
-        <v>1524258</v>
+        <v>96677729</v>
       </c>
       <c r="I45">
-        <v>14978778</v>
+        <v>26455429</v>
       </c>
       <c r="J45">
-        <v>3483</v>
+        <v>6314</v>
       </c>
       <c r="K45">
-        <v>3075030</v>
+        <v>181.3</v>
       </c>
       <c r="L45">
-        <v>79459</v>
-      </c>
-      <c r="M45">
-        <v>65.5</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>620944</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="1">
         <v>45565</v>
       </c>
       <c r="B46">
-        <v>163674</v>
+        <v>1235361</v>
       </c>
       <c r="C46">
-        <v>30163870</v>
+        <v>23730698</v>
       </c>
       <c r="D46">
-        <v>143.7</v>
+        <v>111.8</v>
       </c>
       <c r="E46">
-        <v>4663198</v>
+        <v>10745529</v>
       </c>
       <c r="F46">
-        <v>16197648</v>
+        <v>35430779</v>
       </c>
       <c r="G46">
-        <v>30192833</v>
+        <v>857528</v>
       </c>
       <c r="H46">
-        <v>60396444</v>
+        <v>1761984</v>
       </c>
       <c r="I46">
-        <v>15998792</v>
+        <v>39222886</v>
       </c>
       <c r="J46">
-        <v>4192</v>
+        <v>9636</v>
       </c>
       <c r="K46">
-        <v>5642137</v>
+        <v>310.1</v>
       </c>
       <c r="L46">
-        <v>134535</v>
-      </c>
-      <c r="M46">
-        <v>53.3</v>
-      </c>
-      <c r="N46">
         <v>0</v>
       </c>
-      <c r="O46">
-        <v>682638</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="1">
         <v>45596</v>
       </c>
       <c r="B47">
-        <v>196602</v>
+        <v>1086155</v>
       </c>
       <c r="C47">
-        <v>35522512</v>
+        <v>11109804</v>
       </c>
       <c r="D47">
-        <v>161.2</v>
+        <v>51.8</v>
       </c>
       <c r="E47">
-        <v>187548</v>
+        <v>8707117</v>
       </c>
       <c r="F47">
-        <v>651818</v>
+        <v>29744289</v>
       </c>
       <c r="G47">
-        <v>31522091</v>
+        <v>59103443</v>
       </c>
       <c r="H47">
-        <v>67058369</v>
+        <v>121851425</v>
       </c>
       <c r="I47">
-        <v>29269316</v>
+        <v>17776987</v>
       </c>
       <c r="J47">
-        <v>7174</v>
+        <v>4106</v>
       </c>
       <c r="K47">
-        <v>72094</v>
+        <v>172.2</v>
       </c>
       <c r="L47">
-        <v>1792</v>
-      </c>
-      <c r="M47">
-        <v>24.1</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>794478</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="1">
         <v>45626</v>
       </c>
       <c r="B48">
-        <v>182886</v>
+        <v>1256628</v>
       </c>
       <c r="C48">
-        <v>31314512</v>
+        <v>6584802</v>
       </c>
       <c r="D48">
-        <v>142.7</v>
+        <v>31.5</v>
       </c>
       <c r="E48">
-        <v>3381857</v>
+        <v>16796517</v>
       </c>
       <c r="F48">
-        <v>11530523</v>
+        <v>57517419</v>
       </c>
       <c r="G48">
-        <v>53773885</v>
+        <v>27387869</v>
       </c>
       <c r="H48">
-        <v>114222656</v>
+        <v>54823895</v>
       </c>
       <c r="I48">
-        <v>711008</v>
+        <v>25402297</v>
       </c>
       <c r="J48">
-        <v>179</v>
+        <v>6216</v>
       </c>
       <c r="K48">
-        <v>1187156</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L48">
-        <v>28846</v>
-      </c>
-      <c r="M48">
-        <v>362.5</v>
-      </c>
-      <c r="N48">
-        <v>1.24</v>
-      </c>
-      <c r="O48">
-        <v>940684</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" s="1">
         <v>45657</v>
       </c>
       <c r="B49">
-        <v>232895</v>
+        <v>1263910</v>
       </c>
       <c r="C49">
-        <v>42381352</v>
+        <v>34129292</v>
       </c>
       <c r="D49">
-        <v>199.9</v>
+        <v>151.6</v>
       </c>
       <c r="E49">
-        <v>6654795</v>
+        <v>14577641</v>
       </c>
       <c r="F49">
-        <v>21834366</v>
+        <v>49287630</v>
       </c>
       <c r="G49">
-        <v>78166969</v>
+        <v>71526671</v>
       </c>
       <c r="H49">
-        <v>160907273</v>
+        <v>146098594</v>
       </c>
       <c r="I49">
-        <v>46213859</v>
+        <v>21007754</v>
       </c>
       <c r="J49">
-        <v>10870</v>
+        <v>5023</v>
       </c>
       <c r="K49">
-        <v>4211028</v>
+        <v>247</v>
       </c>
       <c r="L49">
-        <v>106208</v>
-      </c>
-      <c r="M49">
-        <v>262.7</v>
-      </c>
-      <c r="N49">
-        <v>5.75</v>
-      </c>
-      <c r="O49">
-        <v>951182</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="1">
         <v>45688</v>
       </c>
+      <c r="B50">
+        <v>1262958</v>
+      </c>
       <c r="C50">
-        <v>24519941</v>
+        <v>20142956</v>
       </c>
       <c r="D50">
-        <v>120.4</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E50">
-        <v>4383736</v>
+        <v>21778370</v>
       </c>
       <c r="F50">
-        <v>15644612</v>
+        <v>71423892</v>
       </c>
       <c r="G50">
-        <v>41883327</v>
+        <v>53453556</v>
       </c>
       <c r="H50">
-        <v>92725803</v>
+        <v>111124763</v>
       </c>
       <c r="I50">
-        <v>22344499</v>
+        <v>15338783</v>
       </c>
       <c r="J50">
-        <v>5683</v>
+        <v>3724</v>
       </c>
       <c r="K50">
-        <v>3907303</v>
+        <v>171.3</v>
       </c>
       <c r="L50">
-        <v>100069</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="1">
         <v>45716</v>
       </c>
+      <c r="B51">
+        <v>957136</v>
+      </c>
       <c r="C51">
-        <v>24972384</v>
+        <v>34216365</v>
       </c>
       <c r="D51">
-        <v>122.6</v>
+        <v>155</v>
       </c>
       <c r="E51">
-        <v>3838616</v>
+        <v>6423241</v>
       </c>
       <c r="F51">
-        <v>13699196</v>
+        <v>21200977</v>
       </c>
       <c r="G51">
-        <v>39114852</v>
+        <v>735212</v>
       </c>
       <c r="H51">
-        <v>86596655</v>
+        <v>1501412</v>
       </c>
       <c r="I51">
-        <v>22544817</v>
+        <v>481435</v>
       </c>
       <c r="J51">
-        <v>5733</v>
+        <v>113</v>
       </c>
       <c r="K51">
-        <v>3659754</v>
+        <v>229.7</v>
       </c>
       <c r="L51">
-        <v>93729</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>12.48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="1">
         <v>45747</v>
       </c>
+      <c r="B52">
+        <v>1040873</v>
+      </c>
       <c r="C52">
-        <v>20477509</v>
+        <v>22112765</v>
       </c>
       <c r="D52">
-        <v>100.5</v>
+        <v>98.8</v>
       </c>
       <c r="E52">
-        <v>3537935</v>
+        <v>4232502</v>
       </c>
       <c r="F52">
-        <v>12626128</v>
+        <v>14024269</v>
       </c>
       <c r="G52">
-        <v>34506144</v>
+        <v>66565503</v>
       </c>
       <c r="H52">
-        <v>76393404</v>
+        <v>139324097</v>
       </c>
       <c r="I52">
-        <v>21646338</v>
+        <v>23244911</v>
       </c>
       <c r="J52">
-        <v>5505</v>
+        <v>5239</v>
       </c>
       <c r="K52">
-        <v>3031872</v>
+        <v>125</v>
       </c>
       <c r="L52">
-        <v>77648</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="1">
         <v>45777</v>
       </c>
+      <c r="B53">
+        <v>975226</v>
+      </c>
       <c r="C53">
-        <v>21091564</v>
+        <v>11961852</v>
       </c>
       <c r="D53">
-        <v>103.5</v>
+        <v>58.1</v>
       </c>
       <c r="E53">
-        <v>3198932</v>
+        <v>15679716</v>
       </c>
       <c r="F53">
-        <v>11416301</v>
+        <v>50521014</v>
       </c>
       <c r="G53">
-        <v>32702397</v>
+        <v>68468548</v>
       </c>
       <c r="H53">
-        <v>72400074</v>
+        <v>136048855</v>
       </c>
       <c r="I53">
-        <v>21125058</v>
+        <v>11044432</v>
       </c>
       <c r="J53">
-        <v>5372</v>
+        <v>2463</v>
       </c>
       <c r="K53">
-        <v>3382407</v>
+        <v>163.4</v>
       </c>
       <c r="L53">
-        <v>86626</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="1">
         <v>45808</v>
       </c>
+      <c r="B54">
+        <v>810522</v>
+      </c>
       <c r="C54">
-        <v>22388025</v>
+        <v>42260900</v>
       </c>
       <c r="D54">
-        <v>109.9</v>
+        <v>196.4</v>
       </c>
       <c r="E54">
-        <v>3796677</v>
+        <v>9113661</v>
       </c>
       <c r="F54">
-        <v>13549523</v>
+        <v>29710630</v>
       </c>
       <c r="G54">
-        <v>36123760</v>
+        <v>29520860</v>
       </c>
       <c r="H54">
-        <v>79974655</v>
+        <v>61258418</v>
       </c>
       <c r="I54">
-        <v>18236556</v>
+        <v>256264</v>
       </c>
       <c r="J54">
-        <v>4638</v>
+        <v>62</v>
       </c>
       <c r="K54">
-        <v>3789430</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L54">
-        <v>97050</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="1">
         <v>45838</v>
       </c>
+      <c r="B55">
+        <v>823924</v>
+      </c>
       <c r="C55">
-        <v>23170040</v>
+        <v>23678895</v>
       </c>
       <c r="D55">
-        <v>113.7</v>
+        <v>107.2</v>
       </c>
       <c r="E55">
-        <v>3333458</v>
+        <v>10907856</v>
       </c>
       <c r="F55">
-        <v>11896395</v>
+        <v>35575865</v>
       </c>
       <c r="G55">
-        <v>34058782</v>
+        <v>57996158</v>
       </c>
       <c r="H55">
-        <v>75402984</v>
+        <v>113562661</v>
       </c>
       <c r="I55">
-        <v>20172747</v>
+        <v>12171076</v>
       </c>
       <c r="J55">
-        <v>5130</v>
+        <v>2808</v>
       </c>
       <c r="K55">
-        <v>3604309</v>
+        <v>251.7</v>
       </c>
       <c r="L55">
-        <v>92309</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="1">
         <v>45869</v>
       </c>
+      <c r="B56">
+        <v>911441</v>
+      </c>
       <c r="C56">
-        <v>22850507</v>
+        <v>41585256</v>
       </c>
       <c r="D56">
-        <v>112.2</v>
+        <v>180</v>
       </c>
       <c r="E56">
-        <v>3402303</v>
+        <v>9556577</v>
       </c>
       <c r="F56">
-        <v>12142088</v>
+        <v>30780786</v>
       </c>
       <c r="G56">
-        <v>34311063</v>
+        <v>41182565</v>
       </c>
       <c r="H56">
-        <v>75961511</v>
+        <v>87982660</v>
       </c>
       <c r="I56">
-        <v>21049252</v>
+        <v>21911282</v>
       </c>
       <c r="J56">
-        <v>5353</v>
+        <v>4817</v>
       </c>
       <c r="K56">
-        <v>3215550</v>
+        <v>269.1</v>
       </c>
       <c r="L56">
-        <v>82353</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="1">
         <v>45900</v>
       </c>
+      <c r="B57">
+        <v>999790</v>
+      </c>
       <c r="C57">
-        <v>24974216</v>
+        <v>39879973</v>
       </c>
       <c r="D57">
-        <v>122.6</v>
+        <v>169.6</v>
       </c>
       <c r="E57">
-        <v>3885995</v>
+        <v>7240508</v>
       </c>
       <c r="F57">
-        <v>13868280</v>
+        <v>23161716</v>
       </c>
       <c r="G57">
-        <v>29504029</v>
+        <v>365359</v>
       </c>
       <c r="H57">
-        <v>65319185</v>
+        <v>737093</v>
       </c>
       <c r="I57">
-        <v>20039028</v>
+        <v>28226340</v>
       </c>
       <c r="J57">
-        <v>5096</v>
+        <v>6449</v>
       </c>
       <c r="K57">
-        <v>3449841</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L57">
-        <v>88353</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" s="1">
         <v>45930</v>
       </c>
+      <c r="B58">
+        <v>1024288</v>
+      </c>
       <c r="C58">
-        <v>23125931</v>
+        <v>18946919</v>
       </c>
       <c r="D58">
-        <v>113.5</v>
+        <v>85</v>
       </c>
       <c r="E58">
-        <v>3768232</v>
+        <v>12854541</v>
       </c>
       <c r="F58">
-        <v>13448011</v>
+        <v>43540968</v>
       </c>
       <c r="G58">
-        <v>31371616</v>
+        <v>61496127</v>
       </c>
       <c r="H58">
-        <v>69453849</v>
+        <v>126100780</v>
       </c>
       <c r="I58">
-        <v>19054866</v>
+        <v>19040614</v>
       </c>
       <c r="J58">
-        <v>4846</v>
+        <v>4380</v>
       </c>
       <c r="K58">
-        <v>3504922</v>
+        <v>233.5</v>
       </c>
       <c r="L58">
-        <v>89764</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" s="1">
         <v>45961</v>
       </c>
+      <c r="B59">
+        <v>1228879</v>
+      </c>
       <c r="C59">
-        <v>23339330</v>
+        <v>995893</v>
       </c>
       <c r="D59">
-        <v>114.6</v>
+        <v>4.6</v>
       </c>
       <c r="E59">
-        <v>3458543</v>
+        <v>9363987</v>
       </c>
       <c r="F59">
-        <v>12342797</v>
+        <v>28894192</v>
       </c>
       <c r="G59">
-        <v>36363191</v>
+        <v>21260324</v>
       </c>
       <c r="H59">
-        <v>80504733</v>
+        <v>44680047</v>
       </c>
       <c r="I59">
-        <v>19525180</v>
+        <v>36644654</v>
       </c>
       <c r="J59">
-        <v>4966</v>
+        <v>8384</v>
       </c>
       <c r="K59">
-        <v>3529242</v>
+        <v>121.4</v>
       </c>
       <c r="L59">
-        <v>90386</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" s="1">
         <v>45991</v>
       </c>
+      <c r="B60">
+        <v>1400953</v>
+      </c>
       <c r="C60">
-        <v>26912505</v>
+        <v>47554339</v>
       </c>
       <c r="D60">
-        <v>132.1</v>
+        <v>206.5</v>
       </c>
       <c r="E60">
-        <v>4416185</v>
+        <v>21953588</v>
       </c>
       <c r="F60">
-        <v>15760414</v>
+        <v>72295534</v>
       </c>
       <c r="G60">
-        <v>38808773</v>
+        <v>32188759</v>
       </c>
       <c r="H60">
-        <v>85919024</v>
+        <v>66294228</v>
       </c>
       <c r="I60">
-        <v>22067217</v>
+        <v>31027011</v>
       </c>
       <c r="J60">
-        <v>5612</v>
+        <v>7424</v>
       </c>
       <c r="K60">
-        <v>3941572</v>
+        <v>256.5</v>
       </c>
       <c r="L60">
-        <v>100946</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="1">
         <v>46022</v>
       </c>
+      <c r="B61">
+        <v>1330286</v>
+      </c>
       <c r="C61">
-        <v>26807931</v>
+        <v>51743341</v>
       </c>
       <c r="D61">
-        <v>131.6</v>
+        <v>233.3</v>
       </c>
       <c r="E61">
-        <v>4488734</v>
+        <v>15169514</v>
       </c>
       <c r="F61">
-        <v>16019328</v>
+        <v>48106147</v>
       </c>
       <c r="G61">
-        <v>39071129</v>
+        <v>106053050</v>
       </c>
       <c r="H61">
-        <v>86499857</v>
+        <v>212840533</v>
       </c>
       <c r="I61">
-        <v>24908621</v>
+        <v>23861400</v>
       </c>
       <c r="J61">
-        <v>6335</v>
+        <v>5234</v>
       </c>
       <c r="K61">
-        <v>4144756</v>
+        <v>167.2</v>
       </c>
       <c r="L61">
-        <v>106150</v>
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="1">
+        <v>46053</v>
+      </c>
+      <c r="C62">
+        <v>23613905</v>
+      </c>
+      <c r="D62">
+        <v>113.3</v>
+      </c>
+      <c r="E62">
+        <v>9222203</v>
+      </c>
+      <c r="F62">
+        <v>32017019</v>
+      </c>
+      <c r="G62">
+        <v>42051456</v>
+      </c>
+      <c r="H62">
+        <v>90808314</v>
+      </c>
+      <c r="I62">
+        <v>18096983</v>
+      </c>
+      <c r="J62">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C63">
+        <v>23613905</v>
+      </c>
+      <c r="D63">
+        <v>113.3</v>
+      </c>
+      <c r="E63">
+        <v>9222203</v>
+      </c>
+      <c r="F63">
+        <v>32017019</v>
+      </c>
+      <c r="G63">
+        <v>42051456</v>
+      </c>
+      <c r="H63">
+        <v>90808314</v>
+      </c>
+      <c r="I63">
+        <v>18096983</v>
+      </c>
+      <c r="J63">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C64">
+        <v>23613905</v>
+      </c>
+      <c r="D64">
+        <v>113.3</v>
+      </c>
+      <c r="E64">
+        <v>9222203</v>
+      </c>
+      <c r="F64">
+        <v>32017019</v>
+      </c>
+      <c r="G64">
+        <v>42051456</v>
+      </c>
+      <c r="H64">
+        <v>90808314</v>
+      </c>
+      <c r="I64">
+        <v>18096983</v>
+      </c>
+      <c r="J64">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="1">
+        <v>46142</v>
+      </c>
+      <c r="C65">
+        <v>23613905</v>
+      </c>
+      <c r="D65">
+        <v>113.3</v>
+      </c>
+      <c r="E65">
+        <v>9222203</v>
+      </c>
+      <c r="F65">
+        <v>32017019</v>
+      </c>
+      <c r="G65">
+        <v>42051456</v>
+      </c>
+      <c r="H65">
+        <v>90808314</v>
+      </c>
+      <c r="I65">
+        <v>18096983</v>
+      </c>
+      <c r="J65">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="1">
+        <v>46173</v>
+      </c>
+      <c r="C66">
+        <v>23613905</v>
+      </c>
+      <c r="D66">
+        <v>113.3</v>
+      </c>
+      <c r="E66">
+        <v>9222203</v>
+      </c>
+      <c r="F66">
+        <v>32017019</v>
+      </c>
+      <c r="G66">
+        <v>42051456</v>
+      </c>
+      <c r="H66">
+        <v>90808314</v>
+      </c>
+      <c r="I66">
+        <v>18096983</v>
+      </c>
+      <c r="J66">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C67">
+        <v>23613905</v>
+      </c>
+      <c r="D67">
+        <v>113.3</v>
+      </c>
+      <c r="E67">
+        <v>9222203</v>
+      </c>
+      <c r="F67">
+        <v>32017019</v>
+      </c>
+      <c r="G67">
+        <v>42051456</v>
+      </c>
+      <c r="H67">
+        <v>90808314</v>
+      </c>
+      <c r="I67">
+        <v>18096983</v>
+      </c>
+      <c r="J67">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C68">
+        <v>23613905</v>
+      </c>
+      <c r="D68">
+        <v>113.3</v>
+      </c>
+      <c r="E68">
+        <v>9222203</v>
+      </c>
+      <c r="F68">
+        <v>32017019</v>
+      </c>
+      <c r="G68">
+        <v>42051456</v>
+      </c>
+      <c r="H68">
+        <v>90808314</v>
+      </c>
+      <c r="I68">
+        <v>18096983</v>
+      </c>
+      <c r="J68">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C69">
+        <v>23613905</v>
+      </c>
+      <c r="D69">
+        <v>113.3</v>
+      </c>
+      <c r="E69">
+        <v>9222203</v>
+      </c>
+      <c r="F69">
+        <v>32017019</v>
+      </c>
+      <c r="G69">
+        <v>42051456</v>
+      </c>
+      <c r="H69">
+        <v>90808314</v>
+      </c>
+      <c r="I69">
+        <v>18096983</v>
+      </c>
+      <c r="J69">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="1">
+        <v>46295</v>
+      </c>
+      <c r="C70">
+        <v>23613905</v>
+      </c>
+      <c r="D70">
+        <v>113.3</v>
+      </c>
+      <c r="E70">
+        <v>9222203</v>
+      </c>
+      <c r="F70">
+        <v>32017019</v>
+      </c>
+      <c r="G70">
+        <v>42051456</v>
+      </c>
+      <c r="H70">
+        <v>90808314</v>
+      </c>
+      <c r="I70">
+        <v>18096983</v>
+      </c>
+      <c r="J70">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="1">
+        <v>46326</v>
+      </c>
+      <c r="C71">
+        <v>23613905</v>
+      </c>
+      <c r="D71">
+        <v>113.3</v>
+      </c>
+      <c r="E71">
+        <v>9222203</v>
+      </c>
+      <c r="F71">
+        <v>32017019</v>
+      </c>
+      <c r="G71">
+        <v>42051456</v>
+      </c>
+      <c r="H71">
+        <v>90808314</v>
+      </c>
+      <c r="I71">
+        <v>18096983</v>
+      </c>
+      <c r="J71">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="1">
+        <v>46356</v>
+      </c>
+      <c r="C72">
+        <v>23613905</v>
+      </c>
+      <c r="D72">
+        <v>113.3</v>
+      </c>
+      <c r="E72">
+        <v>9222203</v>
+      </c>
+      <c r="F72">
+        <v>32017019</v>
+      </c>
+      <c r="G72">
+        <v>42051456</v>
+      </c>
+      <c r="H72">
+        <v>90808314</v>
+      </c>
+      <c r="I72">
+        <v>18096983</v>
+      </c>
+      <c r="J72">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="1">
+        <v>46387</v>
+      </c>
+      <c r="C73">
+        <v>23613905</v>
+      </c>
+      <c r="D73">
+        <v>113.3</v>
+      </c>
+      <c r="E73">
+        <v>9222203</v>
+      </c>
+      <c r="F73">
+        <v>32017019</v>
+      </c>
+      <c r="G73">
+        <v>42051456</v>
+      </c>
+      <c r="H73">
+        <v>90808314</v>
+      </c>
+      <c r="I73">
+        <v>18096983</v>
+      </c>
+      <c r="J73">
+        <v>4471</v>
       </c>
     </row>
   </sheetData>

--- a/static/sample-data/planning/synth_otc_pharma.xlsx
+++ b/static/sample-data/planning/synth_otc_pharma.xlsx
@@ -385,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -431,7 +431,7 @@
         <v>44227</v>
       </c>
       <c r="B2">
-        <v>949283</v>
+        <v>1808019</v>
       </c>
       <c r="C2">
         <v>17641040</v>
@@ -440,10 +440,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="E2">
-        <v>9990727</v>
+        <v>24976818</v>
       </c>
       <c r="F2">
-        <v>41533780</v>
+        <v>103834450</v>
       </c>
       <c r="G2">
         <v>58854554</v>
@@ -452,10 +452,10 @@
         <v>143346675</v>
       </c>
       <c r="I2">
-        <v>9840605</v>
+        <v>24601513</v>
       </c>
       <c r="J2">
-        <v>2805</v>
+        <v>7012</v>
       </c>
       <c r="K2">
         <v>140.3</v>
@@ -469,7 +469,7 @@
         <v>44255</v>
       </c>
       <c r="B3">
-        <v>1064971</v>
+        <v>2034511</v>
       </c>
       <c r="C3">
         <v>21471519</v>
@@ -478,10 +478,10 @@
         <v>118.3</v>
       </c>
       <c r="E3">
-        <v>8658030</v>
+        <v>21645076</v>
       </c>
       <c r="F3">
-        <v>35968913</v>
+        <v>89922283</v>
       </c>
       <c r="G3">
         <v>80883027</v>
@@ -490,10 +490,10 @@
         <v>193123061</v>
       </c>
       <c r="I3">
-        <v>13361515</v>
+        <v>33403787</v>
       </c>
       <c r="J3">
-        <v>3744</v>
+        <v>9360</v>
       </c>
       <c r="K3">
         <v>162.7</v>
@@ -507,7 +507,7 @@
         <v>44286</v>
       </c>
       <c r="B4">
-        <v>1075622</v>
+        <v>2033975</v>
       </c>
       <c r="C4">
         <v>9949849</v>
@@ -516,10 +516,10 @@
         <v>53.9</v>
       </c>
       <c r="E4">
-        <v>10224360</v>
+        <v>25560900</v>
       </c>
       <c r="F4">
-        <v>40755909</v>
+        <v>101889772</v>
       </c>
       <c r="G4">
         <v>495312</v>
@@ -528,10 +528,10 @@
         <v>1223270</v>
       </c>
       <c r="I4">
-        <v>15522515</v>
+        <v>38806287</v>
       </c>
       <c r="J4">
-        <v>4492</v>
+        <v>11229</v>
       </c>
       <c r="K4">
         <v>208.5</v>
@@ -545,7 +545,7 @@
         <v>44316</v>
       </c>
       <c r="B5">
-        <v>1079551</v>
+        <v>1987509</v>
       </c>
       <c r="C5">
         <v>14913865</v>
@@ -554,10 +554,10 @@
         <v>78.2</v>
       </c>
       <c r="E5">
-        <v>5918930</v>
+        <v>14797325</v>
       </c>
       <c r="F5">
-        <v>23037409</v>
+        <v>57593522</v>
       </c>
       <c r="G5">
         <v>56055601</v>
@@ -566,10 +566,10 @@
         <v>131051401</v>
       </c>
       <c r="I5">
-        <v>21271125</v>
+        <v>53177813</v>
       </c>
       <c r="J5">
-        <v>6121</v>
+        <v>15304</v>
       </c>
       <c r="K5">
         <v>368</v>
@@ -583,7 +583,7 @@
         <v>44347</v>
       </c>
       <c r="B6">
-        <v>1058471</v>
+        <v>1936426</v>
       </c>
       <c r="C6">
         <v>13344175</v>
@@ -592,10 +592,10 @@
         <v>70</v>
       </c>
       <c r="E6">
-        <v>7408942</v>
+        <v>18522354</v>
       </c>
       <c r="F6">
-        <v>29300738</v>
+        <v>73251844</v>
       </c>
       <c r="G6">
         <v>52919109</v>
@@ -604,10 +604,10 @@
         <v>124197276</v>
       </c>
       <c r="I6">
-        <v>19868962</v>
+        <v>49672405</v>
       </c>
       <c r="J6">
-        <v>5830</v>
+        <v>14574</v>
       </c>
       <c r="K6">
         <v>94.40000000000001</v>
@@ -621,7 +621,7 @@
         <v>44377</v>
       </c>
       <c r="B7">
-        <v>1004959</v>
+        <v>1736777</v>
       </c>
       <c r="C7">
         <v>22627392</v>
@@ -630,10 +630,10 @@
         <v>127</v>
       </c>
       <c r="E7">
-        <v>99441</v>
+        <v>248603</v>
       </c>
       <c r="F7">
-        <v>381460</v>
+        <v>953651</v>
       </c>
       <c r="G7">
         <v>18670649</v>
@@ -642,10 +642,10 @@
         <v>48020721</v>
       </c>
       <c r="I7">
-        <v>26050030</v>
+        <v>65125075</v>
       </c>
       <c r="J7">
-        <v>6888</v>
+        <v>17221</v>
       </c>
       <c r="K7">
         <v>104.3</v>
@@ -659,7 +659,7 @@
         <v>44408</v>
       </c>
       <c r="B8">
-        <v>842405</v>
+        <v>1633979</v>
       </c>
       <c r="C8">
         <v>25049369</v>
@@ -668,10 +668,10 @@
         <v>134.6</v>
       </c>
       <c r="E8">
-        <v>9776946</v>
+        <v>24442364</v>
       </c>
       <c r="F8">
-        <v>39252370</v>
+        <v>98130926</v>
       </c>
       <c r="G8">
         <v>34237530</v>
@@ -680,10 +680,10 @@
         <v>83063144</v>
       </c>
       <c r="I8">
-        <v>8005919</v>
+        <v>20014798</v>
       </c>
       <c r="J8">
-        <v>2267</v>
+        <v>5667</v>
       </c>
       <c r="K8">
         <v>69.3</v>
@@ -697,7 +697,7 @@
         <v>44439</v>
       </c>
       <c r="B9">
-        <v>897396</v>
+        <v>1700243</v>
       </c>
       <c r="C9">
         <v>15796079</v>
@@ -706,10 +706,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E9">
-        <v>11477222</v>
+        <v>28693056</v>
       </c>
       <c r="F9">
-        <v>45628941</v>
+        <v>114072353</v>
       </c>
       <c r="G9">
         <v>33354938</v>
@@ -718,10 +718,10 @@
         <v>80608893</v>
       </c>
       <c r="I9">
-        <v>12781072</v>
+        <v>31952680</v>
       </c>
       <c r="J9">
-        <v>3514</v>
+        <v>8786</v>
       </c>
       <c r="K9">
         <v>343.4</v>
@@ -735,7 +735,7 @@
         <v>44469</v>
       </c>
       <c r="B10">
-        <v>896981</v>
+        <v>1736597</v>
       </c>
       <c r="C10">
         <v>13216232</v>
@@ -744,10 +744,10 @@
         <v>69.7</v>
       </c>
       <c r="E10">
-        <v>5032553</v>
+        <v>12581383</v>
       </c>
       <c r="F10">
-        <v>19317126</v>
+        <v>48292814</v>
       </c>
       <c r="G10">
         <v>54433084</v>
@@ -756,10 +756,10 @@
         <v>132857203</v>
       </c>
       <c r="I10">
-        <v>13686631</v>
+        <v>34216578</v>
       </c>
       <c r="J10">
-        <v>3790</v>
+        <v>9476</v>
       </c>
       <c r="K10">
         <v>334</v>
@@ -773,7 +773,7 @@
         <v>44500</v>
       </c>
       <c r="B11">
-        <v>886590</v>
+        <v>1676175</v>
       </c>
       <c r="C11">
         <v>15137218</v>
@@ -782,10 +782,10 @@
         <v>85.5</v>
       </c>
       <c r="E11">
-        <v>201244</v>
+        <v>503111</v>
       </c>
       <c r="F11">
-        <v>771164</v>
+        <v>1927909</v>
       </c>
       <c r="G11">
         <v>34200560</v>
@@ -794,10 +794,10 @@
         <v>83283612</v>
       </c>
       <c r="I11">
-        <v>13977217</v>
+        <v>34943044</v>
       </c>
       <c r="J11">
-        <v>3651</v>
+        <v>9128</v>
       </c>
       <c r="K11">
         <v>330.8</v>
@@ -811,7 +811,7 @@
         <v>44530</v>
       </c>
       <c r="B12">
-        <v>1140317</v>
+        <v>2091549</v>
       </c>
       <c r="C12">
         <v>14767606</v>
@@ -820,10 +820,10 @@
         <v>81</v>
       </c>
       <c r="E12">
-        <v>7505740</v>
+        <v>18764351</v>
       </c>
       <c r="F12">
-        <v>28419982</v>
+        <v>71049955</v>
       </c>
       <c r="G12">
         <v>41484927</v>
@@ -832,10 +832,10 @@
         <v>96374355</v>
       </c>
       <c r="I12">
-        <v>23437241</v>
+        <v>58593102</v>
       </c>
       <c r="J12">
-        <v>6465</v>
+        <v>16163</v>
       </c>
       <c r="K12">
         <v>50.4</v>
@@ -849,7 +849,7 @@
         <v>44561</v>
       </c>
       <c r="B13">
-        <v>1395764</v>
+        <v>2304844</v>
       </c>
       <c r="C13">
         <v>23669579</v>
@@ -858,10 +858,10 @@
         <v>123</v>
       </c>
       <c r="E13">
-        <v>8868024</v>
+        <v>22170061</v>
       </c>
       <c r="F13">
-        <v>32762745</v>
+        <v>81906862</v>
       </c>
       <c r="G13">
         <v>59852953</v>
@@ -870,10 +870,10 @@
         <v>139708244</v>
       </c>
       <c r="I13">
-        <v>35242781</v>
+        <v>88106953</v>
       </c>
       <c r="J13">
-        <v>9616</v>
+        <v>24041</v>
       </c>
       <c r="K13">
         <v>398.4</v>
@@ -887,7 +887,7 @@
         <v>44592</v>
       </c>
       <c r="B14">
-        <v>1177568</v>
+        <v>2208649</v>
       </c>
       <c r="C14">
         <v>23917267</v>
@@ -896,10 +896,10 @@
         <v>124.6</v>
       </c>
       <c r="E14">
-        <v>8386786</v>
+        <v>20966964</v>
       </c>
       <c r="F14">
-        <v>31608793</v>
+        <v>79021983</v>
       </c>
       <c r="G14">
         <v>30276465</v>
@@ -908,10 +908,10 @@
         <v>71238482</v>
       </c>
       <c r="I14">
-        <v>12805753</v>
+        <v>32014383</v>
       </c>
       <c r="J14">
-        <v>3557</v>
+        <v>8894</v>
       </c>
       <c r="K14">
         <v>55.5</v>
@@ -925,7 +925,7 @@
         <v>44620</v>
       </c>
       <c r="B15">
-        <v>1090579</v>
+        <v>2081906</v>
       </c>
       <c r="C15">
         <v>8033476</v>
@@ -934,10 +934,10 @@
         <v>43.9</v>
       </c>
       <c r="E15">
-        <v>8329089</v>
+        <v>20822723</v>
       </c>
       <c r="F15">
-        <v>32251256</v>
+        <v>80628140</v>
       </c>
       <c r="G15">
         <v>56207344</v>
@@ -946,10 +946,10 @@
         <v>132825453</v>
       </c>
       <c r="I15">
-        <v>12772539</v>
+        <v>31931347</v>
       </c>
       <c r="J15">
-        <v>3455</v>
+        <v>8638</v>
       </c>
       <c r="K15">
         <v>104.7</v>
@@ -963,7 +963,7 @@
         <v>44651</v>
       </c>
       <c r="B16">
-        <v>1077450</v>
+        <v>2045412</v>
       </c>
       <c r="C16">
         <v>22084677</v>
@@ -972,10 +972,10 @@
         <v>118.4</v>
       </c>
       <c r="E16">
-        <v>8045114</v>
+        <v>20112784</v>
       </c>
       <c r="F16">
-        <v>30608922</v>
+        <v>76522304</v>
       </c>
       <c r="G16">
         <v>35527721</v>
@@ -984,10 +984,10 @@
         <v>82171553</v>
       </c>
       <c r="I16">
-        <v>17592196</v>
+        <v>43980490</v>
       </c>
       <c r="J16">
-        <v>4528</v>
+        <v>11321</v>
       </c>
       <c r="K16">
         <v>269.5</v>
@@ -1001,7 +1001,7 @@
         <v>44681</v>
       </c>
       <c r="B17">
-        <v>956666</v>
+        <v>1826341</v>
       </c>
       <c r="C17">
         <v>22405328</v>
@@ -1010,10 +1010,10 @@
         <v>119.1</v>
       </c>
       <c r="E17">
-        <v>8570386</v>
+        <v>21425966</v>
       </c>
       <c r="F17">
-        <v>33919343</v>
+        <v>84798358</v>
       </c>
       <c r="G17">
         <v>58799188</v>
@@ -1022,10 +1022,10 @@
         <v>143245499</v>
       </c>
       <c r="I17">
-        <v>9193174</v>
+        <v>22982935</v>
       </c>
       <c r="J17">
-        <v>2566</v>
+        <v>6416</v>
       </c>
       <c r="K17">
         <v>140.2</v>
@@ -1039,7 +1039,7 @@
         <v>44712</v>
       </c>
       <c r="B18">
-        <v>855047</v>
+        <v>1584718</v>
       </c>
       <c r="C18">
         <v>27726375</v>
@@ -1048,10 +1048,10 @@
         <v>147.1</v>
       </c>
       <c r="E18">
-        <v>10177631</v>
+        <v>25444079</v>
       </c>
       <c r="F18">
-        <v>38234669</v>
+        <v>95586673</v>
       </c>
       <c r="G18">
         <v>35940348</v>
@@ -1060,10 +1060,10 @@
         <v>83765859</v>
       </c>
       <c r="I18">
-        <v>6516390</v>
+        <v>16290975</v>
       </c>
       <c r="J18">
-        <v>1787</v>
+        <v>4468</v>
       </c>
       <c r="K18">
         <v>318.7</v>
@@ -1077,7 +1077,7 @@
         <v>44742</v>
       </c>
       <c r="B19">
-        <v>961540</v>
+        <v>1806270</v>
       </c>
       <c r="C19">
         <v>9410294</v>
@@ -1086,10 +1086,10 @@
         <v>48.6</v>
       </c>
       <c r="E19">
-        <v>10732173</v>
+        <v>26830431</v>
       </c>
       <c r="F19">
-        <v>40355993</v>
+        <v>100889982</v>
       </c>
       <c r="G19">
         <v>34242354</v>
@@ -1098,10 +1098,10 @@
         <v>80513452</v>
       </c>
       <c r="I19">
-        <v>18258344</v>
+        <v>45645861</v>
       </c>
       <c r="J19">
-        <v>5058</v>
+        <v>12645</v>
       </c>
       <c r="K19">
         <v>172.6</v>
@@ -1115,7 +1115,7 @@
         <v>44773</v>
       </c>
       <c r="B20">
-        <v>945136</v>
+        <v>1760090</v>
       </c>
       <c r="C20">
         <v>23570227</v>
@@ -1124,10 +1124,10 @@
         <v>125.7</v>
       </c>
       <c r="E20">
-        <v>4832320</v>
+        <v>12080799</v>
       </c>
       <c r="F20">
-        <v>18003657</v>
+        <v>45009143</v>
       </c>
       <c r="G20">
         <v>21948232</v>
@@ -1136,10 +1136,10 @@
         <v>49455673</v>
       </c>
       <c r="I20">
-        <v>21550292</v>
+        <v>53875730</v>
       </c>
       <c r="J20">
-        <v>5762</v>
+        <v>14404</v>
       </c>
       <c r="K20">
         <v>344.2</v>
@@ -1153,7 +1153,7 @@
         <v>44804</v>
       </c>
       <c r="B21">
-        <v>790217</v>
+        <v>1522612</v>
       </c>
       <c r="C21">
         <v>14893056</v>
@@ -1162,10 +1162,10 @@
         <v>72.40000000000001</v>
       </c>
       <c r="E21">
-        <v>7929469</v>
+        <v>19823671</v>
       </c>
       <c r="F21">
-        <v>28610100</v>
+        <v>71525251</v>
       </c>
       <c r="G21">
         <v>24335596</v>
@@ -1174,10 +1174,10 @@
         <v>56204639</v>
       </c>
       <c r="I21">
-        <v>5794313</v>
+        <v>14485783</v>
       </c>
       <c r="J21">
-        <v>1530</v>
+        <v>3826</v>
       </c>
       <c r="K21">
         <v>94.5</v>
@@ -1191,7 +1191,7 @@
         <v>44834</v>
       </c>
       <c r="B22">
-        <v>829040</v>
+        <v>1606040</v>
       </c>
       <c r="C22">
         <v>16461895</v>
@@ -1200,10 +1200,10 @@
         <v>82.3</v>
       </c>
       <c r="E22">
-        <v>5626126</v>
+        <v>14065315</v>
       </c>
       <c r="F22">
-        <v>21233382</v>
+        <v>53083454</v>
       </c>
       <c r="G22">
         <v>34921735</v>
@@ -1212,10 +1212,10 @@
         <v>89887841</v>
       </c>
       <c r="I22">
-        <v>10688201</v>
+        <v>26720501</v>
       </c>
       <c r="J22">
-        <v>2894</v>
+        <v>7234</v>
       </c>
       <c r="K22">
         <v>219.6</v>
@@ -1229,7 +1229,7 @@
         <v>44865</v>
       </c>
       <c r="B23">
-        <v>930965</v>
+        <v>1796938</v>
       </c>
       <c r="C23">
         <v>20263161</v>
@@ -1238,10 +1238,10 @@
         <v>102.7</v>
       </c>
       <c r="E23">
-        <v>4409552</v>
+        <v>11023880</v>
       </c>
       <c r="F23">
-        <v>16178074</v>
+        <v>40445185</v>
       </c>
       <c r="G23">
         <v>42890495</v>
@@ -1250,10 +1250,10 @@
         <v>97700135</v>
       </c>
       <c r="I23">
-        <v>14378383</v>
+        <v>35945957</v>
       </c>
       <c r="J23">
-        <v>3886</v>
+        <v>9716</v>
       </c>
       <c r="K23">
         <v>63.9</v>
@@ -1267,7 +1267,7 @@
         <v>44895</v>
       </c>
       <c r="B24">
-        <v>940814</v>
+        <v>1627488</v>
       </c>
       <c r="C24">
         <v>837225</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>15328017</v>
+        <v>38320043</v>
       </c>
       <c r="F24">
-        <v>54736294</v>
+        <v>136840736</v>
       </c>
       <c r="G24">
         <v>46752701</v>
@@ -1288,10 +1288,10 @@
         <v>109067177</v>
       </c>
       <c r="I24">
-        <v>101213</v>
+        <v>253034</v>
       </c>
       <c r="J24">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="K24">
         <v>157.4</v>
@@ -1305,7 +1305,7 @@
         <v>44926</v>
       </c>
       <c r="B25">
-        <v>1269946</v>
+        <v>2273868</v>
       </c>
       <c r="C25">
         <v>36333495</v>
@@ -1314,10 +1314,10 @@
         <v>187.5</v>
       </c>
       <c r="E25">
-        <v>9626837</v>
+        <v>24067091</v>
       </c>
       <c r="F25">
-        <v>36260798</v>
+        <v>90651995</v>
       </c>
       <c r="G25">
         <v>889591</v>
@@ -1326,10 +1326,10 @@
         <v>1966297</v>
       </c>
       <c r="I25">
-        <v>30347624</v>
+        <v>75869060</v>
       </c>
       <c r="J25">
-        <v>7957</v>
+        <v>19892</v>
       </c>
       <c r="K25">
         <v>113</v>
@@ -1343,7 +1343,7 @@
         <v>44957</v>
       </c>
       <c r="B26">
-        <v>1251873</v>
+        <v>2282379</v>
       </c>
       <c r="C26">
         <v>16474954</v>
@@ -1352,10 +1352,10 @@
         <v>83.7</v>
       </c>
       <c r="E26">
-        <v>11268245</v>
+        <v>28170613</v>
       </c>
       <c r="F26">
-        <v>39432611</v>
+        <v>98581528</v>
       </c>
       <c r="G26">
         <v>62391592</v>
@@ -1364,10 +1364,10 @@
         <v>146415657</v>
       </c>
       <c r="I26">
-        <v>19667175</v>
+        <v>49167937</v>
       </c>
       <c r="J26">
-        <v>5144</v>
+        <v>12860</v>
       </c>
       <c r="K26">
         <v>68.40000000000001</v>
@@ -1381,7 +1381,7 @@
         <v>44985</v>
       </c>
       <c r="B27">
-        <v>1177561</v>
+        <v>2197015</v>
       </c>
       <c r="C27">
         <v>35963214</v>
@@ -1390,10 +1390,10 @@
         <v>182.6</v>
       </c>
       <c r="E27">
-        <v>8307741</v>
+        <v>20769352</v>
       </c>
       <c r="F27">
-        <v>31319706</v>
+        <v>78299265</v>
       </c>
       <c r="G27">
         <v>43436438</v>
@@ -1402,10 +1402,10 @@
         <v>96929517</v>
       </c>
       <c r="I27">
-        <v>18753655</v>
+        <v>46884136</v>
       </c>
       <c r="J27">
-        <v>4649</v>
+        <v>11623</v>
       </c>
       <c r="K27">
         <v>118.4</v>
@@ -1419,7 +1419,7 @@
         <v>45016</v>
       </c>
       <c r="B28">
-        <v>1074621</v>
+        <v>2044445</v>
       </c>
       <c r="C28">
         <v>14732803</v>
@@ -1428,10 +1428,10 @@
         <v>69.7</v>
       </c>
       <c r="E28">
-        <v>6184392</v>
+        <v>15460981</v>
       </c>
       <c r="F28">
-        <v>22196525</v>
+        <v>55491312</v>
       </c>
       <c r="G28">
         <v>26434051</v>
@@ -1440,10 +1440,10 @@
         <v>59540959</v>
       </c>
       <c r="I28">
-        <v>17194311</v>
+        <v>42985777</v>
       </c>
       <c r="J28">
-        <v>4389</v>
+        <v>10972</v>
       </c>
       <c r="K28">
         <v>71</v>
@@ -1457,7 +1457,7 @@
         <v>45046</v>
       </c>
       <c r="B29">
-        <v>820287</v>
+        <v>1536289</v>
       </c>
       <c r="C29">
         <v>8457375</v>
@@ -1466,10 +1466,10 @@
         <v>43.3</v>
       </c>
       <c r="E29">
-        <v>208362</v>
+        <v>520906</v>
       </c>
       <c r="F29">
-        <v>748360</v>
+        <v>1870900</v>
       </c>
       <c r="G29">
         <v>27212819</v>
@@ -1478,10 +1478,10 @@
         <v>62607911</v>
       </c>
       <c r="I29">
-        <v>6960783</v>
+        <v>17401957</v>
       </c>
       <c r="J29">
-        <v>1867</v>
+        <v>4667</v>
       </c>
       <c r="K29">
         <v>91.2</v>
@@ -1495,7 +1495,7 @@
         <v>45077</v>
       </c>
       <c r="B30">
-        <v>847560</v>
+        <v>1635435</v>
       </c>
       <c r="C30">
         <v>18095173</v>
@@ -1504,10 +1504,10 @@
         <v>86.3</v>
       </c>
       <c r="E30">
-        <v>4901535</v>
+        <v>12253837</v>
       </c>
       <c r="F30">
-        <v>17598270</v>
+        <v>43995675</v>
       </c>
       <c r="G30">
         <v>22833027</v>
@@ -1516,10 +1516,10 @@
         <v>52179546</v>
       </c>
       <c r="I30">
-        <v>16506408</v>
+        <v>41266020</v>
       </c>
       <c r="J30">
-        <v>4265</v>
+        <v>10664</v>
       </c>
       <c r="K30">
         <v>256.2</v>
@@ -1533,7 +1533,7 @@
         <v>45107</v>
       </c>
       <c r="B31">
-        <v>803900</v>
+        <v>1563553</v>
       </c>
       <c r="C31">
         <v>21260723</v>
@@ -1542,10 +1542,10 @@
         <v>105.2</v>
       </c>
       <c r="E31">
-        <v>8269036</v>
+        <v>20672591</v>
       </c>
       <c r="F31">
-        <v>29298062</v>
+        <v>73245155</v>
       </c>
       <c r="G31">
         <v>54785896</v>
@@ -1554,10 +1554,10 @@
         <v>118940850</v>
       </c>
       <c r="I31">
-        <v>11209465</v>
+        <v>28023662</v>
       </c>
       <c r="J31">
-        <v>2741</v>
+        <v>6854</v>
       </c>
       <c r="K31">
         <v>318.7</v>
@@ -1571,7 +1571,7 @@
         <v>45138</v>
       </c>
       <c r="B32">
-        <v>949795</v>
+        <v>1791333</v>
       </c>
       <c r="C32">
         <v>11908583</v>
@@ -1580,10 +1580,10 @@
         <v>58.8</v>
       </c>
       <c r="E32">
-        <v>9792485</v>
+        <v>24481213</v>
       </c>
       <c r="F32">
-        <v>35994043</v>
+        <v>89985107</v>
       </c>
       <c r="G32">
         <v>68358420</v>
@@ -1592,10 +1592,10 @@
         <v>144412149</v>
       </c>
       <c r="I32">
-        <v>20833720</v>
+        <v>52084299</v>
       </c>
       <c r="J32">
-        <v>5329</v>
+        <v>13321</v>
       </c>
       <c r="K32">
         <v>85.8</v>
@@ -1609,7 +1609,7 @@
         <v>45169</v>
       </c>
       <c r="B33">
-        <v>953778</v>
+        <v>1793402</v>
       </c>
       <c r="C33">
         <v>28691858</v>
@@ -1618,10 +1618,10 @@
         <v>146.3</v>
       </c>
       <c r="E33">
-        <v>5990470</v>
+        <v>14976175</v>
       </c>
       <c r="F33">
-        <v>21403617</v>
+        <v>53509042</v>
       </c>
       <c r="G33">
         <v>33318369</v>
@@ -1630,10 +1630,10 @@
         <v>73818889</v>
       </c>
       <c r="I33">
-        <v>20201562</v>
+        <v>50503906</v>
       </c>
       <c r="J33">
-        <v>5151</v>
+        <v>12879</v>
       </c>
       <c r="K33">
         <v>146.4</v>
@@ -1647,7 +1647,7 @@
         <v>45199</v>
       </c>
       <c r="B34">
-        <v>917061</v>
+        <v>1767428</v>
       </c>
       <c r="C34">
         <v>31308641</v>
@@ -1656,10 +1656,10 @@
         <v>164.6</v>
       </c>
       <c r="E34">
-        <v>6056845</v>
+        <v>15142113</v>
       </c>
       <c r="F34">
-        <v>22379819</v>
+        <v>55949547</v>
       </c>
       <c r="G34">
         <v>59582686</v>
@@ -1668,10 +1668,10 @@
         <v>134392348</v>
       </c>
       <c r="I34">
-        <v>14332272</v>
+        <v>35830680</v>
       </c>
       <c r="J34">
-        <v>3623</v>
+        <v>9058</v>
       </c>
       <c r="K34">
         <v>253.3</v>
@@ -1685,7 +1685,7 @@
         <v>45230</v>
       </c>
       <c r="B35">
-        <v>968383</v>
+        <v>1867466</v>
       </c>
       <c r="C35">
         <v>17770707</v>
@@ -1694,10 +1694,10 @@
         <v>85.3</v>
       </c>
       <c r="E35">
-        <v>8432198</v>
+        <v>21080495</v>
       </c>
       <c r="F35">
-        <v>29189548</v>
+        <v>72973869</v>
       </c>
       <c r="G35">
         <v>24055367</v>
@@ -1706,10 +1706,10 @@
         <v>52389461</v>
       </c>
       <c r="I35">
-        <v>14461448</v>
+        <v>36153619</v>
       </c>
       <c r="J35">
-        <v>3696</v>
+        <v>9241</v>
       </c>
       <c r="K35">
         <v>171.8</v>
@@ -1723,7 +1723,7 @@
         <v>45260</v>
       </c>
       <c r="B36">
-        <v>1201431</v>
+        <v>2168261</v>
       </c>
       <c r="C36">
         <v>22670668</v>
@@ -1732,10 +1732,10 @@
         <v>117.2</v>
       </c>
       <c r="E36">
-        <v>12496754</v>
+        <v>31241886</v>
       </c>
       <c r="F36">
-        <v>42298023</v>
+        <v>105745057</v>
       </c>
       <c r="G36">
         <v>1053986</v>
@@ -1744,10 +1744,10 @@
         <v>2378663</v>
       </c>
       <c r="I36">
-        <v>26306903</v>
+        <v>65767258</v>
       </c>
       <c r="J36">
-        <v>6857</v>
+        <v>17142</v>
       </c>
       <c r="K36">
         <v>37.3</v>
@@ -1761,7 +1761,7 @@
         <v>45291</v>
       </c>
       <c r="B37">
-        <v>1017663</v>
+        <v>1933632</v>
       </c>
       <c r="C37">
         <v>58511876</v>
@@ -1770,10 +1770,10 @@
         <v>278.9</v>
       </c>
       <c r="E37">
-        <v>154988</v>
+        <v>387469</v>
       </c>
       <c r="F37">
-        <v>536716</v>
+        <v>1341789</v>
       </c>
       <c r="G37">
         <v>57985608</v>
@@ -1782,10 +1782,10 @@
         <v>128459081</v>
       </c>
       <c r="I37">
-        <v>11189456</v>
+        <v>27973640</v>
       </c>
       <c r="J37">
-        <v>2871</v>
+        <v>7178</v>
       </c>
       <c r="K37">
         <v>170.5</v>
@@ -1799,7 +1799,7 @@
         <v>45322</v>
       </c>
       <c r="B38">
-        <v>1303786</v>
+        <v>2314867</v>
       </c>
       <c r="C38">
         <v>14988278</v>
@@ -1808,10 +1808,10 @@
         <v>74.40000000000001</v>
       </c>
       <c r="E38">
-        <v>22504469</v>
+        <v>56261172</v>
       </c>
       <c r="F38">
-        <v>77008249</v>
+        <v>192520621</v>
       </c>
       <c r="G38">
         <v>62224047</v>
@@ -1820,10 +1820,10 @@
         <v>138155102</v>
       </c>
       <c r="I38">
-        <v>22052338</v>
+        <v>55130844</v>
       </c>
       <c r="J38">
-        <v>5573</v>
+        <v>13932</v>
       </c>
       <c r="K38">
         <v>156.9</v>
@@ -1837,7 +1837,7 @@
         <v>45351</v>
       </c>
       <c r="B39">
-        <v>1423359</v>
+        <v>2393930</v>
       </c>
       <c r="C39">
         <v>29355932</v>
@@ -1846,10 +1846,10 @@
         <v>149.8</v>
       </c>
       <c r="E39">
-        <v>10730526</v>
+        <v>26826315</v>
       </c>
       <c r="F39">
-        <v>38398963</v>
+        <v>95997407</v>
       </c>
       <c r="G39">
         <v>59171138</v>
@@ -1858,10 +1858,10 @@
         <v>130332530</v>
       </c>
       <c r="I39">
-        <v>34784164</v>
+        <v>86960410</v>
       </c>
       <c r="J39">
-        <v>8423</v>
+        <v>21057</v>
       </c>
       <c r="K39">
         <v>98.7</v>
@@ -1875,7 +1875,7 @@
         <v>45382</v>
       </c>
       <c r="B40">
-        <v>1076087</v>
+        <v>2046966</v>
       </c>
       <c r="C40">
         <v>35691979</v>
@@ -1884,10 +1884,10 @@
         <v>174.1</v>
       </c>
       <c r="E40">
-        <v>5360918</v>
+        <v>13402294</v>
       </c>
       <c r="F40">
-        <v>18725435</v>
+        <v>46813587</v>
       </c>
       <c r="G40">
         <v>59584446</v>
@@ -1896,10 +1896,10 @@
         <v>128715991</v>
       </c>
       <c r="I40">
-        <v>13266132</v>
+        <v>33165331</v>
       </c>
       <c r="J40">
-        <v>3209</v>
+        <v>8024</v>
       </c>
       <c r="K40">
         <v>103.6</v>
@@ -1913,7 +1913,7 @@
         <v>45412</v>
       </c>
       <c r="B41">
-        <v>1015008</v>
+        <v>1915405</v>
       </c>
       <c r="C41">
         <v>29526289</v>
@@ -1922,10 +1922,10 @@
         <v>138.8</v>
       </c>
       <c r="E41">
-        <v>5196253</v>
+        <v>12990634</v>
       </c>
       <c r="F41">
-        <v>19219292</v>
+        <v>48048229</v>
       </c>
       <c r="G41">
         <v>17511373</v>
@@ -1934,10 +1934,10 @@
         <v>38372110</v>
       </c>
       <c r="I41">
-        <v>21138934</v>
+        <v>52847334</v>
       </c>
       <c r="J41">
-        <v>5085</v>
+        <v>12713</v>
       </c>
       <c r="K41">
         <v>370.3</v>
@@ -1951,7 +1951,7 @@
         <v>45443</v>
       </c>
       <c r="B42">
-        <v>874381</v>
+        <v>1708858</v>
       </c>
       <c r="C42">
         <v>32881749</v>
@@ -1960,10 +1960,10 @@
         <v>155.3</v>
       </c>
       <c r="E42">
-        <v>6160934</v>
+        <v>15402334</v>
       </c>
       <c r="F42">
-        <v>21626914</v>
+        <v>54067285</v>
       </c>
       <c r="G42">
         <v>879536</v>
@@ -1972,10 +1972,10 @@
         <v>1910358</v>
       </c>
       <c r="I42">
-        <v>14892581</v>
+        <v>37231452</v>
       </c>
       <c r="J42">
-        <v>3763</v>
+        <v>9408</v>
       </c>
       <c r="K42">
         <v>284.4</v>
@@ -1989,7 +1989,7 @@
         <v>45473</v>
       </c>
       <c r="B43">
-        <v>915650</v>
+        <v>1750057</v>
       </c>
       <c r="C43">
         <v>35976598</v>
@@ -1998,10 +1998,10 @@
         <v>167.4</v>
       </c>
       <c r="E43">
-        <v>8109294</v>
+        <v>20273236</v>
       </c>
       <c r="F43">
-        <v>28004926</v>
+        <v>70012315</v>
       </c>
       <c r="G43">
         <v>45999731</v>
@@ -2010,10 +2010,10 @@
         <v>99473505</v>
       </c>
       <c r="I43">
-        <v>18562608</v>
+        <v>46406520</v>
       </c>
       <c r="J43">
-        <v>4708</v>
+        <v>11770</v>
       </c>
       <c r="K43">
         <v>239.2</v>
@@ -2027,7 +2027,7 @@
         <v>45504</v>
       </c>
       <c r="B44">
-        <v>802813</v>
+        <v>1557528</v>
       </c>
       <c r="C44">
         <v>24481732</v>
@@ -2036,10 +2036,10 @@
         <v>114.8</v>
       </c>
       <c r="E44">
-        <v>8337865</v>
+        <v>20844663</v>
       </c>
       <c r="F44">
-        <v>28498152</v>
+        <v>71245379</v>
       </c>
       <c r="G44">
         <v>28215233</v>
@@ -2048,10 +2048,10 @@
         <v>61505150</v>
       </c>
       <c r="I44">
-        <v>9353655</v>
+        <v>23384137</v>
       </c>
       <c r="J44">
-        <v>2343</v>
+        <v>5856</v>
       </c>
       <c r="K44">
         <v>164.9</v>
@@ -2065,7 +2065,7 @@
         <v>45535</v>
       </c>
       <c r="B45">
-        <v>1021665</v>
+        <v>1875879</v>
       </c>
       <c r="C45">
         <v>34434451</v>
@@ -2074,10 +2074,10 @@
         <v>166</v>
       </c>
       <c r="E45">
-        <v>10351683</v>
+        <v>25879207</v>
       </c>
       <c r="F45">
-        <v>36796012</v>
+        <v>91990031</v>
       </c>
       <c r="G45">
         <v>45275003</v>
@@ -2086,10 +2086,10 @@
         <v>96677729</v>
       </c>
       <c r="I45">
-        <v>26455429</v>
+        <v>66138573</v>
       </c>
       <c r="J45">
-        <v>6314</v>
+        <v>15785</v>
       </c>
       <c r="K45">
         <v>181.3</v>
@@ -2103,7 +2103,7 @@
         <v>45565</v>
       </c>
       <c r="B46">
-        <v>1235361</v>
+        <v>2018306</v>
       </c>
       <c r="C46">
         <v>23730698</v>
@@ -2112,10 +2112,10 @@
         <v>111.8</v>
       </c>
       <c r="E46">
-        <v>10745529</v>
+        <v>26863822</v>
       </c>
       <c r="F46">
-        <v>35430779</v>
+        <v>88576946</v>
       </c>
       <c r="G46">
         <v>857528</v>
@@ -2124,10 +2124,10 @@
         <v>1761984</v>
       </c>
       <c r="I46">
-        <v>39222886</v>
+        <v>98057215</v>
       </c>
       <c r="J46">
-        <v>9636</v>
+        <v>24091</v>
       </c>
       <c r="K46">
         <v>310.1</v>
@@ -2141,7 +2141,7 @@
         <v>45596</v>
       </c>
       <c r="B47">
-        <v>1086155</v>
+        <v>2017306</v>
       </c>
       <c r="C47">
         <v>11109804</v>
@@ -2150,10 +2150,10 @@
         <v>51.8</v>
       </c>
       <c r="E47">
-        <v>8707117</v>
+        <v>21767792</v>
       </c>
       <c r="F47">
-        <v>29744289</v>
+        <v>74360722</v>
       </c>
       <c r="G47">
         <v>59103443</v>
@@ -2162,10 +2162,10 @@
         <v>121851425</v>
       </c>
       <c r="I47">
-        <v>17776987</v>
+        <v>44442467</v>
       </c>
       <c r="J47">
-        <v>4106</v>
+        <v>10266</v>
       </c>
       <c r="K47">
         <v>172.2</v>
@@ -2179,7 +2179,7 @@
         <v>45626</v>
       </c>
       <c r="B48">
-        <v>1256628</v>
+        <v>2213712</v>
       </c>
       <c r="C48">
         <v>6584802</v>
@@ -2188,10 +2188,10 @@
         <v>31.5</v>
       </c>
       <c r="E48">
-        <v>16796517</v>
+        <v>41991292</v>
       </c>
       <c r="F48">
-        <v>57517419</v>
+        <v>143793547</v>
       </c>
       <c r="G48">
         <v>27387869</v>
@@ -2200,10 +2200,10 @@
         <v>54823895</v>
       </c>
       <c r="I48">
-        <v>25402297</v>
+        <v>63505741</v>
       </c>
       <c r="J48">
-        <v>6216</v>
+        <v>15540</v>
       </c>
       <c r="K48">
         <v>81.59999999999999</v>
@@ -2217,7 +2217,7 @@
         <v>45657</v>
       </c>
       <c r="B49">
-        <v>1263910</v>
+        <v>2264363</v>
       </c>
       <c r="C49">
         <v>34129292</v>
@@ -2226,10 +2226,10 @@
         <v>151.6</v>
       </c>
       <c r="E49">
-        <v>14577641</v>
+        <v>36444103</v>
       </c>
       <c r="F49">
-        <v>49287630</v>
+        <v>123219076</v>
       </c>
       <c r="G49">
         <v>71526671</v>
@@ -2238,10 +2238,10 @@
         <v>146098594</v>
       </c>
       <c r="I49">
-        <v>21007754</v>
+        <v>52519386</v>
       </c>
       <c r="J49">
-        <v>5023</v>
+        <v>12558</v>
       </c>
       <c r="K49">
         <v>247</v>
@@ -2255,7 +2255,7 @@
         <v>45688</v>
       </c>
       <c r="B50">
-        <v>1262958</v>
+        <v>2236364</v>
       </c>
       <c r="C50">
         <v>20142956</v>
@@ -2264,10 +2264,10 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E50">
-        <v>21778370</v>
+        <v>54445925</v>
       </c>
       <c r="F50">
-        <v>71423892</v>
+        <v>178559729</v>
       </c>
       <c r="G50">
         <v>53453556</v>
@@ -2276,10 +2276,10 @@
         <v>111124763</v>
       </c>
       <c r="I50">
-        <v>15338783</v>
+        <v>38346958</v>
       </c>
       <c r="J50">
-        <v>3724</v>
+        <v>9309</v>
       </c>
       <c r="K50">
         <v>171.3</v>
@@ -2293,7 +2293,7 @@
         <v>45716</v>
       </c>
       <c r="B51">
-        <v>957136</v>
+        <v>1701881</v>
       </c>
       <c r="C51">
         <v>34216365</v>
@@ -2302,10 +2302,10 @@
         <v>155</v>
       </c>
       <c r="E51">
-        <v>6423241</v>
+        <v>16058102</v>
       </c>
       <c r="F51">
-        <v>21200977</v>
+        <v>53002443</v>
       </c>
       <c r="G51">
         <v>735212</v>
@@ -2314,10 +2314,10 @@
         <v>1501412</v>
       </c>
       <c r="I51">
-        <v>481435</v>
+        <v>1203587</v>
       </c>
       <c r="J51">
-        <v>113</v>
+        <v>282</v>
       </c>
       <c r="K51">
         <v>229.7</v>
@@ -2331,7 +2331,7 @@
         <v>45747</v>
       </c>
       <c r="B52">
-        <v>1040873</v>
+        <v>1990316</v>
       </c>
       <c r="C52">
         <v>22112765</v>
@@ -2340,10 +2340,10 @@
         <v>98.8</v>
       </c>
       <c r="E52">
-        <v>4232502</v>
+        <v>10581256</v>
       </c>
       <c r="F52">
-        <v>14024269</v>
+        <v>35060671</v>
       </c>
       <c r="G52">
         <v>66565503</v>
@@ -2352,10 +2352,10 @@
         <v>139324097</v>
       </c>
       <c r="I52">
-        <v>23244911</v>
+        <v>58112279</v>
       </c>
       <c r="J52">
-        <v>5239</v>
+        <v>13099</v>
       </c>
       <c r="K52">
         <v>125</v>
@@ -2369,7 +2369,7 @@
         <v>45777</v>
       </c>
       <c r="B53">
-        <v>975226</v>
+        <v>1829830</v>
       </c>
       <c r="C53">
         <v>11961852</v>
@@ -2378,10 +2378,10 @@
         <v>58.1</v>
       </c>
       <c r="E53">
-        <v>15679716</v>
+        <v>39199289</v>
       </c>
       <c r="F53">
-        <v>50521014</v>
+        <v>126302536</v>
       </c>
       <c r="G53">
         <v>68468548</v>
@@ -2390,10 +2390,10 @@
         <v>136048855</v>
       </c>
       <c r="I53">
-        <v>11044432</v>
+        <v>27611080</v>
       </c>
       <c r="J53">
-        <v>2463</v>
+        <v>6157</v>
       </c>
       <c r="K53">
         <v>163.4</v>
@@ -2407,7 +2407,7 @@
         <v>45808</v>
       </c>
       <c r="B54">
-        <v>810522</v>
+        <v>1401882</v>
       </c>
       <c r="C54">
         <v>42260900</v>
@@ -2416,10 +2416,10 @@
         <v>196.4</v>
       </c>
       <c r="E54">
-        <v>9113661</v>
+        <v>22784152</v>
       </c>
       <c r="F54">
-        <v>29710630</v>
+        <v>74276576</v>
       </c>
       <c r="G54">
         <v>29520860</v>
@@ -2428,10 +2428,10 @@
         <v>61258418</v>
       </c>
       <c r="I54">
-        <v>256264</v>
+        <v>640660</v>
       </c>
       <c r="J54">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="K54">
         <v>82.90000000000001</v>
@@ -2445,7 +2445,7 @@
         <v>45838</v>
       </c>
       <c r="B55">
-        <v>823924</v>
+        <v>1546251</v>
       </c>
       <c r="C55">
         <v>23678895</v>
@@ -2454,10 +2454,10 @@
         <v>107.2</v>
       </c>
       <c r="E55">
-        <v>10907856</v>
+        <v>27269639</v>
       </c>
       <c r="F55">
-        <v>35575865</v>
+        <v>88939662</v>
       </c>
       <c r="G55">
         <v>57996158</v>
@@ -2466,10 +2466,10 @@
         <v>113562661</v>
       </c>
       <c r="I55">
-        <v>12171076</v>
+        <v>30427689</v>
       </c>
       <c r="J55">
-        <v>2808</v>
+        <v>7019</v>
       </c>
       <c r="K55">
         <v>251.7</v>
@@ -2483,7 +2483,7 @@
         <v>45869</v>
       </c>
       <c r="B56">
-        <v>911441</v>
+        <v>1739837</v>
       </c>
       <c r="C56">
         <v>41585256</v>
@@ -2492,10 +2492,10 @@
         <v>180</v>
       </c>
       <c r="E56">
-        <v>9556577</v>
+        <v>23891442</v>
       </c>
       <c r="F56">
-        <v>30780786</v>
+        <v>76951964</v>
       </c>
       <c r="G56">
         <v>41182565</v>
@@ -2504,10 +2504,10 @@
         <v>87982660</v>
       </c>
       <c r="I56">
-        <v>21911282</v>
+        <v>54778204</v>
       </c>
       <c r="J56">
-        <v>4817</v>
+        <v>12043</v>
       </c>
       <c r="K56">
         <v>269.1</v>
@@ -2521,7 +2521,7 @@
         <v>45900</v>
       </c>
       <c r="B57">
-        <v>999790</v>
+        <v>1835140</v>
       </c>
       <c r="C57">
         <v>39879973</v>
@@ -2530,10 +2530,10 @@
         <v>169.6</v>
       </c>
       <c r="E57">
-        <v>7240508</v>
+        <v>18101271</v>
       </c>
       <c r="F57">
-        <v>23161716</v>
+        <v>57904290</v>
       </c>
       <c r="G57">
         <v>365359</v>
@@ -2542,10 +2542,10 @@
         <v>737093</v>
       </c>
       <c r="I57">
-        <v>28226340</v>
+        <v>70565850</v>
       </c>
       <c r="J57">
-        <v>6449</v>
+        <v>16123</v>
       </c>
       <c r="K57">
         <v>65.09999999999999</v>
@@ -2559,7 +2559,7 @@
         <v>45930</v>
       </c>
       <c r="B58">
-        <v>1024288</v>
+        <v>1907299</v>
       </c>
       <c r="C58">
         <v>18946919</v>
@@ -2568,10 +2568,10 @@
         <v>85</v>
       </c>
       <c r="E58">
-        <v>12854541</v>
+        <v>32136353</v>
       </c>
       <c r="F58">
-        <v>43540968</v>
+        <v>108852420</v>
       </c>
       <c r="G58">
         <v>61496127</v>
@@ -2580,10 +2580,10 @@
         <v>126100780</v>
       </c>
       <c r="I58">
-        <v>19040614</v>
+        <v>47601536</v>
       </c>
       <c r="J58">
-        <v>4380</v>
+        <v>10950</v>
       </c>
       <c r="K58">
         <v>233.5</v>
@@ -2597,7 +2597,7 @@
         <v>45961</v>
       </c>
       <c r="B59">
-        <v>1228879</v>
+        <v>2107071</v>
       </c>
       <c r="C59">
         <v>995893</v>
@@ -2606,10 +2606,10 @@
         <v>4.6</v>
       </c>
       <c r="E59">
-        <v>9363987</v>
+        <v>23409969</v>
       </c>
       <c r="F59">
-        <v>28894192</v>
+        <v>72235480</v>
       </c>
       <c r="G59">
         <v>21260324</v>
@@ -2618,10 +2618,10 @@
         <v>44680047</v>
       </c>
       <c r="I59">
-        <v>36644654</v>
+        <v>91611636</v>
       </c>
       <c r="J59">
-        <v>8384</v>
+        <v>20960</v>
       </c>
       <c r="K59">
         <v>121.4</v>
@@ -2635,7 +2635,7 @@
         <v>45991</v>
       </c>
       <c r="B60">
-        <v>1400953</v>
+        <v>2298650</v>
       </c>
       <c r="C60">
         <v>47554339</v>
@@ -2644,10 +2644,10 @@
         <v>206.5</v>
       </c>
       <c r="E60">
-        <v>21953588</v>
+        <v>54883969</v>
       </c>
       <c r="F60">
-        <v>72295534</v>
+        <v>180738835</v>
       </c>
       <c r="G60">
         <v>32188759</v>
@@ -2656,10 +2656,10 @@
         <v>66294228</v>
       </c>
       <c r="I60">
-        <v>31027011</v>
+        <v>77567528</v>
       </c>
       <c r="J60">
-        <v>7424</v>
+        <v>18560</v>
       </c>
       <c r="K60">
         <v>256.5</v>
@@ -2673,7 +2673,7 @@
         <v>46022</v>
       </c>
       <c r="B61">
-        <v>1330286</v>
+        <v>2333119</v>
       </c>
       <c r="C61">
         <v>51743341</v>
@@ -2682,10 +2682,10 @@
         <v>233.3</v>
       </c>
       <c r="E61">
-        <v>15169514</v>
+        <v>37923784</v>
       </c>
       <c r="F61">
-        <v>48106147</v>
+        <v>120265369</v>
       </c>
       <c r="G61">
         <v>106053050</v>
@@ -2694,10 +2694,10 @@
         <v>212840533</v>
       </c>
       <c r="I61">
-        <v>23861400</v>
+        <v>59653501</v>
       </c>
       <c r="J61">
-        <v>5234</v>
+        <v>13084</v>
       </c>
       <c r="K61">
         <v>167.2</v>
@@ -2717,10 +2717,10 @@
         <v>113.3</v>
       </c>
       <c r="E62">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F62">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G62">
         <v>42051456</v>
@@ -2729,10 +2729,10 @@
         <v>90808314</v>
       </c>
       <c r="I62">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J62">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -2746,10 +2746,10 @@
         <v>113.3</v>
       </c>
       <c r="E63">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F63">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G63">
         <v>42051456</v>
@@ -2758,10 +2758,10 @@
         <v>90808314</v>
       </c>
       <c r="I63">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J63">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -2775,10 +2775,10 @@
         <v>113.3</v>
       </c>
       <c r="E64">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F64">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G64">
         <v>42051456</v>
@@ -2787,10 +2787,10 @@
         <v>90808314</v>
       </c>
       <c r="I64">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J64">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2804,10 +2804,10 @@
         <v>113.3</v>
       </c>
       <c r="E65">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F65">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G65">
         <v>42051456</v>
@@ -2816,10 +2816,10 @@
         <v>90808314</v>
       </c>
       <c r="I65">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J65">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2833,10 +2833,10 @@
         <v>113.3</v>
       </c>
       <c r="E66">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F66">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G66">
         <v>42051456</v>
@@ -2845,10 +2845,10 @@
         <v>90808314</v>
       </c>
       <c r="I66">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J66">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2862,10 +2862,10 @@
         <v>113.3</v>
       </c>
       <c r="E67">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F67">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G67">
         <v>42051456</v>
@@ -2874,10 +2874,10 @@
         <v>90808314</v>
       </c>
       <c r="I67">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J67">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2891,10 +2891,10 @@
         <v>113.3</v>
       </c>
       <c r="E68">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F68">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G68">
         <v>42051456</v>
@@ -2903,10 +2903,10 @@
         <v>90808314</v>
       </c>
       <c r="I68">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J68">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2920,10 +2920,10 @@
         <v>113.3</v>
       </c>
       <c r="E69">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F69">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G69">
         <v>42051456</v>
@@ -2932,10 +2932,10 @@
         <v>90808314</v>
       </c>
       <c r="I69">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J69">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2949,10 +2949,10 @@
         <v>113.3</v>
       </c>
       <c r="E70">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F70">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G70">
         <v>42051456</v>
@@ -2961,10 +2961,10 @@
         <v>90808314</v>
       </c>
       <c r="I70">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J70">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2978,10 +2978,10 @@
         <v>113.3</v>
       </c>
       <c r="E71">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F71">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G71">
         <v>42051456</v>
@@ -2990,10 +2990,10 @@
         <v>90808314</v>
       </c>
       <c r="I71">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J71">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3007,10 +3007,10 @@
         <v>113.3</v>
       </c>
       <c r="E72">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F72">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G72">
         <v>42051456</v>
@@ -3019,10 +3019,10 @@
         <v>90808314</v>
       </c>
       <c r="I72">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J72">
-        <v>4471</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3036,10 +3036,10 @@
         <v>113.3</v>
       </c>
       <c r="E73">
-        <v>9222203</v>
+        <v>23055508</v>
       </c>
       <c r="F73">
-        <v>32017019</v>
+        <v>80042549</v>
       </c>
       <c r="G73">
         <v>42051456</v>
@@ -3048,10 +3048,184 @@
         <v>90808314</v>
       </c>
       <c r="I73">
-        <v>18096983</v>
+        <v>45242459</v>
       </c>
       <c r="J73">
-        <v>4471</v>
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="1">
+        <v>46418</v>
+      </c>
+      <c r="C74">
+        <v>23613905</v>
+      </c>
+      <c r="D74">
+        <v>113.3</v>
+      </c>
+      <c r="E74">
+        <v>23055508</v>
+      </c>
+      <c r="F74">
+        <v>80042549</v>
+      </c>
+      <c r="G74">
+        <v>42051456</v>
+      </c>
+      <c r="H74">
+        <v>90808314</v>
+      </c>
+      <c r="I74">
+        <v>45242459</v>
+      </c>
+      <c r="J74">
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="1">
+        <v>46446</v>
+      </c>
+      <c r="C75">
+        <v>23613905</v>
+      </c>
+      <c r="D75">
+        <v>113.3</v>
+      </c>
+      <c r="E75">
+        <v>23055508</v>
+      </c>
+      <c r="F75">
+        <v>80042549</v>
+      </c>
+      <c r="G75">
+        <v>42051456</v>
+      </c>
+      <c r="H75">
+        <v>90808314</v>
+      </c>
+      <c r="I75">
+        <v>45242459</v>
+      </c>
+      <c r="J75">
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="1">
+        <v>46477</v>
+      </c>
+      <c r="C76">
+        <v>23613905</v>
+      </c>
+      <c r="D76">
+        <v>113.3</v>
+      </c>
+      <c r="E76">
+        <v>23055508</v>
+      </c>
+      <c r="F76">
+        <v>80042549</v>
+      </c>
+      <c r="G76">
+        <v>42051456</v>
+      </c>
+      <c r="H76">
+        <v>90808314</v>
+      </c>
+      <c r="I76">
+        <v>45242459</v>
+      </c>
+      <c r="J76">
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="1">
+        <v>46507</v>
+      </c>
+      <c r="C77">
+        <v>23613905</v>
+      </c>
+      <c r="D77">
+        <v>113.3</v>
+      </c>
+      <c r="E77">
+        <v>23055508</v>
+      </c>
+      <c r="F77">
+        <v>80042549</v>
+      </c>
+      <c r="G77">
+        <v>42051456</v>
+      </c>
+      <c r="H77">
+        <v>90808314</v>
+      </c>
+      <c r="I77">
+        <v>45242459</v>
+      </c>
+      <c r="J77">
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="1">
+        <v>46538</v>
+      </c>
+      <c r="C78">
+        <v>23613905</v>
+      </c>
+      <c r="D78">
+        <v>113.3</v>
+      </c>
+      <c r="E78">
+        <v>23055508</v>
+      </c>
+      <c r="F78">
+        <v>80042549</v>
+      </c>
+      <c r="G78">
+        <v>42051456</v>
+      </c>
+      <c r="H78">
+        <v>90808314</v>
+      </c>
+      <c r="I78">
+        <v>45242459</v>
+      </c>
+      <c r="J78">
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="1">
+        <v>46568</v>
+      </c>
+      <c r="C79">
+        <v>23613905</v>
+      </c>
+      <c r="D79">
+        <v>113.3</v>
+      </c>
+      <c r="E79">
+        <v>23055508</v>
+      </c>
+      <c r="F79">
+        <v>80042549</v>
+      </c>
+      <c r="G79">
+        <v>42051456</v>
+      </c>
+      <c r="H79">
+        <v>90808314</v>
+      </c>
+      <c r="I79">
+        <v>45242459</v>
+      </c>
+      <c r="J79">
+        <v>11178</v>
       </c>
     </row>
   </sheetData>
